--- a/review/termenverkenning.xlsx
+++ b/review/termenverkenning.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,35 +429,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_gemeenten</t>
+          <t>n_gemeenten_corpus</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>n_passages</t>
+          <t>n_passages_corpus</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sectietype_verdeling</t>
+          <t>n_gemeenten_filter</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>domein_verdeling</t>
+          <t>n_passages_filter</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>categorie_verdeling (heel corpus)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>voorbeeld_gemeente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>voorbeeld_pad</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>voorbeeld_tekst</t>
         </is>
@@ -473,33 +478,32 @@
         <v>339</v>
       </c>
       <c r="C2" t="n">
-        <v>3516</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>artikel=2491; bijlage=462; toelichting_artikel=313; toelichting_algemeen=75; aanhef=62; begrippen=59; bijlage_pdf=38; ondertekening=16</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>wmo=3079; beide=255; jeugd=144; onbekend=38</t>
-        </is>
+        <v>3543</v>
+      </c>
+      <c r="D2" t="n">
+        <v>331</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GM0796</t>
+          <t>kern=2991; twijfel=164; aanbod=164; jeugd=129; buiten_scope=88; waardering=7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bijlage &gt; 9. Zorgt ervoor dat een calamiteit of geweldsincident (artikel 3.4. lid 1 Wmo 2015) binnen 3 dagen wordt gemeld via</t>
+          <t>Moerdijk</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meldpunt Toezicht Wmo - GGD Hart voor Brabant (ggdhvb.nl)
-.
-10. Verstrekt bij en naar aanleiding van een melding aan de toezichthoudende ambtenaar de gegevens die voor het onderzoeken van de melding noodzakelijk zijn. Hieronder ook begrepen de persoonsgegevens, gegevens betreffende de gezondheid en </t>
+          <t>Hoofdstuk 2 Afwegingskaders om te komen tot een maatwerkoplossing &gt; 2.8 Begeleiding: ontwikkeling, stabilisatie, verminderde zelfredzaamheid en logeerzorg &gt; Artikel 2.8.1. Afwegingskader &gt; deel 6</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Vervolgens beoordeelt het College of in het gesprek alle voorliggende voorzieningen zijn meegenomen. Alvorens een maatwerkvoorziening op grond van de Wmo te verstrekken is het van belang om na te gaan wat de mogelijkheden van behandeling zijn. Soms kunnen een maatwerkvoorziening Wmo (begeleiding) en</t>
         </is>
       </c>
     </row>
@@ -509,21 +513,22 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>GM0213</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1. Algemeen &gt; 1.1 Toelichting gebruikte begrippen &gt; deel 2</t>
+          <t>Dinkelland</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>- Niet (of niet veel) duurder is dan vergelijkbare producten, diensten, activiteiten of andere maatregelen;
-- Kan worden bekostigd door iemand met een inkomen op minimumniveau.
-In individuele gevallen kan een voorziening die op zichzelf als algemeen gebruikelijk kan worden beschouwd, vanwege omstand</t>
+          <t>Hoofdstuk 4: Ambities &gt; 4.2 Versterking van samenwerking mantelzorg &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>“Het versterken en verbeteren van de samenwerking met alle betrokken partijen rondom mantelzorg door samenwerking overzichtelijker te maken en beter op elkaar af te stemmen.”
+Waarom is deze ambitie belangrijk?
+Uit het behoefteonderzoek en de Startfoto mantelzorg blijkt dat mantelzorgers knelpunten e</t>
         </is>
       </c>
     </row>
@@ -533,19 +538,20 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>GM1960</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Toelichting &gt; Artikel 1 &gt; Lid 1 onderdeel n: sociaal netwerk</t>
+          <t>Veldhoven</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tot het sociale netwerk worden gerekend de personen uit de huiselijke kring (o.a. (ex-)partners, gezinsleden, familieleden of mantelzorgers) en andere personen met wie iemand een sociale relatie onderhoudt. Met dat laatste worden personen bedoeld met wie de jeugdige en/of ouder(s) regelmatig contact</t>
+          <t>Hoofdstuk 2: Toepassingsbereik, melding en onderzoek &gt; Artikel 6. Onderzoek &gt; lid 6</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6. Als dit nodig is voor het onderzoek, wordt er onafhankelijk sociaal/medisch of bouwkundig advies opgevraagd bij de door de gemeente aangewezen deskundige. Dit advies kan gaan over de situatie van de cliënt en/of zijn mantelzorgers, personen uit zijn leefeenheid of netwerk.</t>
         </is>
       </c>
     </row>
@@ -555,21 +561,21 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>GM0579</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 3</t>
+          <t>Dantumadiel</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>• Hoeveel tijd heeft de mantelzorger? Heeft iemand een baan, een eigen gezin, een ander familielid dat zorg behoeft? Voorbeeld: een echtgenoot wordt ziek, terwijl zijn vrouw ook al voor haar ouders zorgt.
-• Is de zorg te plannen of is er continue controle en toezicht nodig?
-• Hoe is de prognose? (Ee</t>
+          <t>Artikel 3. ONDERZOEK EN IDENTIFICATIE- INLICHTINGEN- EN MEDEWERKINGSPLICHT &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1. Een gesprek maakt deel uit van het onderzoek. Het college onderzoekt in samenspraak met degene of namens wie de melding is gedaan, dan wel diens vertegenwoordiger en waar mogelijk met de mantelzorger of mantelzorgers en desgewenst familie, zo spoedig mogelijk en voor zover nodig:
+a) de behoeften,</t>
         </is>
       </c>
     </row>
@@ -579,19 +585,20 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>GM0147</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 8</t>
+          <t>Rucphen</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brussencursus | Doel: In de cursus leren de jonge mantelzorgers onder andere hoe zij hun emoties kunnen uiten, eigen grenzen kunnen aangeven en hoe zij kunnen omgaan met de thuissituatie. Onderdeel van de cursus zijn een intakegesprek en een ouderbijeenkomst.; Doelgroep: De brussencursus is bedoeld </t>
+          <t>Artikel 1 &gt; lid 3 &gt; Artikel 5. Gesprek</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Deze bepaling is opgenomen om een zorgvuldige procedure te waarborgen. Het kan worden gezien als een uitwerking van de verplichte delegatiebepaling van artikel 2.1.3, eerste lid en tweede lid, onder a, van de wet. Hierin is onder meer bepaald dat de gemeente in de verordening in ieder geval regels v</t>
         </is>
       </c>
     </row>
@@ -605,31 +612,34 @@
         <v>336</v>
       </c>
       <c r="C7" t="n">
-        <v>2519</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>artikel=1854; toelichting_artikel=232; bijlage=200; begrippen=96; toelichting_algemeen=67; aanhef=44; bijlage_pdf=23; ondertekening=3</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>wmo=1595; jeugd=703; beide=198; onbekend=23</t>
-        </is>
+        <v>2530</v>
+      </c>
+      <c r="D7" t="n">
+        <v>322</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GM1674</t>
+          <t>kern=1544; jeugd=675; aanbod=213; twijfel=73; buiten_scope=25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.2.18 Meerjarensubsidie Alzheimercafe 2018 t/m 2021 &gt; Artikel 2 Activiteiten die voor subsidie in aanmerking komen</t>
+          <t>West Betuwe</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Het organiseren van (bijeenkomsten vanuit) een Alzheimer Café waarbij de organisatie faciliteert in advies, informatie en cliëntondersteuning aan mensen met alzheimer maar ook hun mantelzorgers en direct betrokkenen. Ook is het café een plek waar lotgenoten met elkaar in contact komen.</t>
+          <t>Toelichting &gt; Artikel 1 &gt; Lid 1 onder a. aanvraag &gt; deel 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Lid 1 onder c. andere voorziening:
+Een andere voorziening is een voorziening die de inwoner kan ontvangen op grond van een andere wet dan de Wmo, bijvoorbeeld de Zorgverzekeringswet of de Wet langdurige zorg. Een andere voorziening is voorliggend op een Wmo-voorziening.
+Lid 1 onder d. beleidsregels:</t>
         </is>
       </c>
     </row>
@@ -639,20 +649,20 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>GM0189</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.2 Relatie met andere ontwikkelingen &gt; deel 2</t>
+          <t>Zevenaar</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Decentralisatie middelen MEE
-Op dit moment zijn gemeenten op grond van de Wmo verantwoordelijk voor de cliëntondersteuning van alle burgers en ze richten zich met name op ouderen en de ggz-doelgroep. In de huidige situatie wordt de cliëntondersteuning voor mensen met een handicap nog uitgevoerd door</t>
+          <t>Artikel 3 Cliëntondersteuning &gt; lid 2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Het college wijst de inwoner en, indien van toepassing, zijn mantelzorger of vertegenwoordiger voor het onderzoek, bedoeld in artikel 2.3.2 lid 1 Wmo 2015, op de mogelijkheid gebruik te maken van gratis cliëntondersteuning en de mogelijkheid zich tijdens het gesprek te laten bijstaan.</t>
         </is>
       </c>
     </row>
@@ -662,26 +672,20 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>GM0599</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bijlage 1 (pdf) &gt; 3. Thuiswonende mbo-studenten, die geen startkwalificatie lijken te gaan halen en problemen</t>
+          <t>Hillegom</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>werk professionals. contractering
-professionals
-Hulp bij de Alle Bij voorkeur Geen Subsidiëring of Nvt
-thuisadministratie / Rotterdamme gerund door contractering
-financiën en rs vrijwilligers met professionals.
-juridische kwesties professionals
-(sociaal juridische Kostprijs
-dienstverlening) professi</t>
+          <t>HOOFDSTUK 2 – DE AANVRAAG &gt; Artikel 3. Cliëntondersteuning &gt; lid 1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Het College zorgt ervoor dat ingezetenen een beroep kunnen doen op kosteloze cliëntondersteuning, waarbij het belang van de cliënt uitgangspunt is.</t>
         </is>
       </c>
     </row>
@@ -691,19 +695,25 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>GM0118</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bijlage &gt; Lid 5</t>
+          <t>West Maas en Waal</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Het college wijst jeugdigen en ouders op de mogelijkheid om gebruik te maken van cliëntondersteuning. Cliëntondersteuning is onafhankelijke ondersteuning door middel van informatie, advies en algemene ondersteuning die bijdraagt aan het versterken van de zelfredzaamheid en participatie en het verkri</t>
+          <t>Artikel 6. Regels voor bijdrage in de kosten van maatwerkvoorzieningen en
+                                algemene voorzieningen &gt; lid 1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Een cliënt is een bijdrage in de kosten verschuldigd:
+a. voor het gebruik van een algemene voorziening, niet zijnde
+                                        cliëntondersteuning, en,
+b. voor een maatwerkvoorziening dan wel pgb, zolang hij van de
+                                        maatwerkvoorzien</t>
         </is>
       </c>
     </row>
@@ -713,19 +723,20 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>GM0189</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.1 Taken en verantwoordelijkheden gemeenten</t>
+          <t>Stede Broec</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Gemeenten worden verantwoordelijk voor ondersteuning van zelfredzaamheid en maatschappelijke participatie van mensen met een beperking, chronisch psychische of psychosociale problemen. Het streven is daarbij dat mensen zo lang mogelijk in hun eigen leefomgeving (kunnen) blijven (wonen). Ook moeten d</t>
+          <t>Hoofdstuk 2 Toegang &gt; Artikel 2.3 Melding van een hulpvraag &gt; lid 2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>De ontvangst van de melding wordt schriftelijk bevestigd met aanvullend de mogelijkheid voor het indienen van een persoonlijk plan alsmede de mogelijkheid voor onafhankelijke cliëntondersteuning.</t>
         </is>
       </c>
     </row>
@@ -740,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,35 +762,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_gemeenten</t>
+          <t>n_gemeenten_corpus</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>n_passages</t>
+          <t>n_passages_corpus</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sectietype_verdeling</t>
+          <t>n_gemeenten_filter</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>domein_verdeling</t>
+          <t>n_passages_filter</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>categorie_verdeling (heel corpus)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>voorbeeld_gemeente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>voorbeeld_pad</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>voorbeeld_tekst</t>
         </is>
@@ -795,31 +811,33 @@
         <v>283</v>
       </c>
       <c r="C2" t="n">
-        <v>916</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>artikel=487; bijlage=305; toelichting_artikel=86; toelichting_algemeen=20; ondertekening=7; aanhef=5; bijlage_pdf=5; begrippen=1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>wmo=569; jeugd=276; beide=66; onbekend=5</t>
-        </is>
+        <v>918</v>
+      </c>
+      <c r="D2" t="n">
+        <v>161</v>
+      </c>
+      <c r="E2" t="n">
+        <v>297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GM1991</t>
+          <t>kern=593; jeugd=251; twijfel=51; aanbod=15; buiten_scope=8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bijlage &gt; Onderdeel B:</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.2 | De aanbieder betrekt, indien van toepassing, met toestemming van de cliënt, de mantelzorger(s) bij het opstellen van het trajectplan voor cliënt, maakt daarbij gebruik van de ervaringsdeskundigheid van de mantelzorger(s) en neemt in het trajectplan op welke informele zorg (mantelzorg) wordt in</t>
+          <t>Hoofdstuk 1 Kernbegrippen &gt; 1.6 Ondersteuning die gebruikelijk of verplicht is &gt; Artikel 1.6.1 Gebruikelijke hulp in de Wmo 2015 &gt; deel 4</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• wat de relatie is tot degene die ondersteuning nodig heeft. Van een minderjarig kind kan minder verwacht worden dan van een meerderjarig kind;
+• bij ondersteuning door kinderen en jongvolwassen: de leeftijd, vaardigheden, belastbaarheid en leerbaarheid van het kind dan wel jongvolwassene. Daarbij </t>
         </is>
       </c>
     </row>
@@ -829,19 +847,20 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>GM1659</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bijlage &gt; 3. Volgende vraag: ‘Wat is de verwachting van de ontwikkeling in de situatie van de cliënt?</t>
+          <t>Borne</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zelfinzicht | Cliënt heeft zicht op eigen problematiek en herkent wanneer het nodig is hulp te vragen. | Cliënt heeft zicht op eigen problematiek, maar herkent niet altijd wanneer het nodig is hulp te vragen. | Cliënt heeft beperkt tot geen inzicht in eigen problematiek en herkent vaak niet wanneer </t>
+          <t>Hoofdstuk 5. Afweging en voorwaarden maatwerkvoorzieningen &gt; Artikel 5.1 Criteria maatwerkvoorzieningen &gt; lid 3 &gt; deel 6</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Mantelzorg betreft ondersteuning voor een naaste ten behoeve van diens zelfredzaamheid en participatie, die qua omvang en intensiteit de gebruikelijke hulp overstijgt en die rechtstreeks voortkomt uit de sociale relatie tussen personen. Mantelzorg wordt niet verleend in het kader van een hulpverlene</t>
         </is>
       </c>
     </row>
@@ -851,19 +870,20 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>GM1721</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ondertekening &gt; 6. Overige eisen</t>
+          <t>Westervoort</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.2 | De aanbieder betrekt, indien van toepassing, met toestemming van de cliënt, de mantelzorger(s) bij het opstellen van het trajectplan voor cliënt, maakt daarbij gebruik van de ervaringsdeskundigheid van de mantelzorger(s) en neemt in het trajectplan op welke informele zorg (mantelzorg) wordt in</t>
+          <t>Hoofdstuk 3 Toegang tot maatwerkvoorzieningen &gt; Artikel 3.1.5. Mantelzorg &gt; lid 5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Met enige regelmaat wordt de situatie van de cliënt en die van de mantelzorger beoordeeld. Dit zorgt ervoor dat de belastbaarheid van de mantelzorger goed in het oog wordt gehouden en dat overbelasting zoveel mogelijk wordt voorkomen. Inzet van respijtzorg kan de draagkracht van de mantelzorger vers</t>
         </is>
       </c>
     </row>
@@ -873,19 +893,21 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>GM1709</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Toelichting &gt; Artikel 2.4 &gt; Artikel 2.4 (gesprek)</t>
+          <t>Koggenland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Het is van groot belang dat het onderzoek in goede samenspraak met de cliënt plaatsvindt, alleen dan kan goed in kaart worden gebracht wat iemands problemen zijn, wat zijn leefomstandigheden en zijn sociale omgeving (gezin en sociaal netwerk) zijn en wat de mogelijke oplossingen daarvoor zijn. Bij h</t>
+          <t>3. Begeleiding en verzorging &gt; Artikel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>• De redelijkheid bepaalt wat als gebruikelijke hulp kan worden geduid.
+• Wat redelijk is hangt af van de specifieke situatie van een cliënt en zijn huisgenoten. Iedere situatie is anders: maatwerk is nodig. Kan de last (naar algemeen aanvaarde opvattingen) in redelijkheid gedragen worden door de hu</t>
         </is>
       </c>
     </row>
@@ -895,20 +917,20 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>GM1652</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bijlage &gt; 3. Volgende vraag: ‘Wat is de verwachting van de ontwikkeling in de situatie van de cliënt?</t>
+          <t>Achtkarspelen</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>| Individuele Begeleiding Behoudgericht 1 (Lichte problematiek); Lichte problematiek, weinig mogelijkheden tot verbetering, primair behoudgericht
-Cliëntkenmerken | De cliënt heeft lichte problematiek, waarbij ondersteuning nodig is op één of enkele leefgebieden. Er is sprake van weinig mogelijkheden</t>
+          <t>3 Algemeen afwegingskader maatwerkvoorziening &gt; 3.2. Ondersteuning door mantelzorgers en vrijwilligers</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Wanneer verminderde zelfredzaamheid of een participatieprobleem (gedeeltelijk) kan worden opgelost door een mantelzorger of vrijwilliger, kan aanvullend daarop een algemene of maatwerkvoorziening nodig zijn. Bij het bepalen van de meest passende ondersteuningsvorm wordt nadrukkelijk rekening gehoude</t>
         </is>
       </c>
     </row>
@@ -922,34 +944,32 @@
         <v>342</v>
       </c>
       <c r="C7" t="n">
-        <v>4736</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>artikel=3526; bijlage=764; toelichting_artikel=251; toelichting_algemeen=74; aanhef=57; bijlage_pdf=24; begrippen=21; ondertekening=19</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>wmo=2483; jeugd=1807; beide=422; onbekend=24</t>
-        </is>
+        <v>4755</v>
+      </c>
+      <c r="D7" t="n">
+        <v>323</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2072</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GM0613</t>
+          <t>kern=2891; jeugd=1624; twijfel=116; aanbod=91; buiten_scope=27; waardering=6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hoofdstuk 5 Voorwaarden individuele voorzieningen jeugdhulp &gt; Artikel 5.2 Eigen mogelijkheden en probleemoplossend vermogen &gt; lid 3</t>
+          <t>Noordoostpolder</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Uit het onderzoek kan evenwel blijken dat de eigen mogelijkheden en het probleemoplossend vermogen van de ouder(s) tekortschiet, omdat sprake is van:
-a. geobjectiveerde beperkingen om noodzakelijke hulp te bieden; of
-b. een gebrek aan kennis of vaardigheden om noodzakelijke hulp te bieden; of
-c. ove</t>
+          <t>Hoofdstuk 5 Mantelzorg &gt; Artikel 5.3 Ondersteuning mantelzorg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>De ondersteuning aan de mantelzorger geeft geen aanspraak op een maatwerkvoorziening (RBNHO:2017:1022). Het college moet wel onderzoek doen naar de vraag of er de behoefte is aan maatregelen ter ondersteuning zodat de mantelzorger de taken uit kan blijven voeren. Dat behoort tot de wettelijke opdrac</t>
         </is>
       </c>
     </row>
@@ -959,19 +979,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>GM0331</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3 Thema’s en doelen &gt; Doelen &gt; 2. Overbelasting van mantelzorgers wordt voorkomen</t>
+          <t>Almelo</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Mantelzorg is onbetaalde en langdurige zorg voor familieleden of vrienden. Dit kan verzorging zijn of hulp bij dagelijkse activiteiten. Mantelzorgers hebben een waardevolle rol. Door hun inzet kunnen inwoners langer thuis wonen en meedoen in de samenleving. Het is belangrijk dat mantelzorgers worden</t>
+          <t>Hoofdstuk 1: Begripsbepalingen en algemene bepalingen &gt; Artikel 1.1 Begrippen: &gt; lid 1 &gt; deel 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>m. Melding: melding van een behoefte aan maatschappelijke ondersteuning, als bedoeld in artikel 2.3.2 eerste lid 1 Wmo 2015;
+n. Ondersteuning: hulp bij de zelfredzaamheid en de participatie van personen met een beperking of met chronische psychische of psychosociale problemen zoveel mogelijk in de e</t>
         </is>
       </c>
     </row>
@@ -981,20 +1003,23 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>GM0613</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1. Afwegingskader Jeugdhulp &gt; 1.2 Eigen verantwoordelijkheid en probleemoplossend vermogen &gt; Artikel 1.2.1 Onvoldoende eigen mogelijkheden en probleemoplossend vermogen</t>
+          <t>Raalte</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Het kan zijn dat het ouders op het moment van onderzoek niet lukt om alle hulp zelf te bieden. Het kan zijn door overbelasting (niet samenhangend met de zorg aan het kind), door werk, door gebrek aan vaardigheden, door eigen problematiek, etc.
-Wat hebben ouders nodig om het wel te kunnen, of om meer</t>
+          <t>Hoofdstuk 4. Gezond en veilig opgroeien &gt; Artikel 4.5 Beoordeling eigen mogelijkheden en probleemoplossend vermogen &gt; lid 6</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bij de beoordeling van (dreigende) overbelasting betrekt de gemeente in ieder geval:
+a. de behoefte en mogelijkheden van de jeugdige;
+b. de duur van de benodigde inzet, waarbij als uitgangspunt geldt dat kortdurende inzet van niet langer dan drie maanden in een jaar niet leidt tot overbelasting;
+c. </t>
         </is>
       </c>
     </row>
@@ -1004,20 +1029,23 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>GM0267</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hoofdstuk 3: Aanvraag maatwerkvoorziening &gt; Artikel 3.2.2 Gebruikelijke hulp &gt; deel 2</t>
+          <t>Leiden</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bij overbelasting zijn we alert als een inwoner deze voorziening wil in de vorm van een pgb. De taken en verantwoordelijkheden die het beheer van een pgb met zich mee brengen zorgen voor extra belasting. Er wordt nadrukkelijk gemeten of de mantelzorger deze belasting kan dragen.
-Gebruikelijke hulp i</t>
+          <t>Hoofdstuk 8 Maatwerkvoorziening via pgb &gt; Artikel 30 Het pgb voor niet-professionele hulp &gt; deel 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5.
+Geen pgb bij dreigende overbelasting.
+Wanneer ondersteuning wordt ingezet in situaties waarin sprake is van (dreigende) overbelasting, zal zorgvuldig gekeken worden of het inzetten van pgb de juiste oplossing is.
+Wanneer sprake is van inzet vanuit het sociale netwerk kan in zeer uitzonderlijke ge</t>
         </is>
       </c>
     </row>
@@ -1027,21 +1055,20 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>GM0118</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.11.1 Gebruikelijke hulp &gt; deel 2</t>
+          <t>Katwijk</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Voor kinderen die tot het meerpersoonshuishouden behoren, gelden de volgende uitgangspunten:
-1. Kinderen tot 5 jaar leveren geen bijdrage aan de huishouding.
-2. Kinderen van 5 tot 13 jaar worden naar hun eigen mogelijkheden betrokken bij lichte huishoudelijke werkzaamheden zoals opruimen, tafel dekk</t>
+          <t>HOOFDSTUK 2. MAATWERKVOORZIENINGEN &gt; Kortdurend verblijf &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Kortdurend verblijf is bedoeld voor cliënten die permanent toezicht nodig hebben. Bij kortdurend verblijf logeert een cliënt maximaal 72 uur per week in een instelling, bijvoorbeeld in een instelling voor mensen met een beperking, verpleeghuis of verzorgingshuis. Hiermee wordt de mantelzorger (bijv.</t>
         </is>
       </c>
     </row>
@@ -1055,33 +1082,32 @@
         <v>338</v>
       </c>
       <c r="C12" t="n">
-        <v>3196</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>artikel=2271; bijlage=471; toelichting_artikel=251; toelichting_algemeen=78; aanhef=60; begrippen=41; bijlage_pdf=22; ondertekening=2</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>wmo=1834; jeugd=1119; beide=221; onbekend=22</t>
-        </is>
+        <v>3227</v>
+      </c>
+      <c r="D12" t="n">
+        <v>246</v>
+      </c>
+      <c r="E12" t="n">
+        <v>872</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GM1714</t>
+          <t>kern=1300; jeugd=1017; buiten_scope=484; twijfel=320; aanbod=106</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hoofdstuk 2 Draagkracht &gt; Artikel 5. Draagkrachtperiode &gt; lid 3</t>
+          <t>Meppel</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3. In afwijking van lid 1 wordt in geval van een stabiel inkomen in de volgende situaties de draagkracht voor 36 maanden vastgesteld:
-a. Belanghebbende(n) zonder draagkracht die de pensioengerechtigde leeftijd hebben bereikt of;
-b. Belanghebbende(n) zonder draagkracht met een IOAW/IOAZ- of WAO-uitke</t>
+          <t>5. Overige taken in het Sociaal domein &gt; 5.4. Bijzondere bijstand &gt; Artikel 5.4.4. Draagkracht &gt; lid 2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>De draagkrachtperiode geldt voor de duur van twaalf maanden, gerekend vanaf de eerste dag van de maand waarin de kosten worden gemaakt.</t>
         </is>
       </c>
     </row>
@@ -1091,22 +1117,24 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>GM0441</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hoofdstuk 8 Afspraken tussen inwoners en gemeente &gt; 8.1 Terugvordering, invordering en verhaal Participatiewet, Ioaw, Ioaz &gt; Artikel 8.1.21 Afzien van het opleggen van een verhaalsbijdrage</t>
+          <t>Oosterhout</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Link met 8.3 Terugvordering uitkering en artikel 8.3.1 Terugvordering en incasso
-Wij stellen de verhaalsbijdrage op nihil als:
-a. de op te leggen verhaalsbijdrage lager is dan € 50,00 per maand;
-b. de onderhoudsplichtige bijstand ontvangt, of een inkomen uit arbeid ontvangt dat gelijk is aan de voor</t>
+          <t>Welke persoonsgegevens?</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Indien noodzakelijk voor de toegang kunnen de volgende categorieën persoonsgegevens door de Sociaal Team Uitvoering worden verwerkt.
+De Cliënt:
+• naam, geboortedatum, geboorteplaats, geslacht, adres, woonplaats, postcode;
+• burgerservicenummer;
+• contactgegevens (zoals telefoonnummer en e-mailadres)</t>
         </is>
       </c>
     </row>
@@ -1116,20 +1144,20 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>GM0994</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 3</t>
+          <t>Wijk bij Duurstede</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-de zieke partner/huisgenoot zich in de terminale levensfase bevindt.
-Er wordt daarbij telkens onderzoek gedaan naar de verhouding tussen draagkracht en draaglast van de individuele cliënt. Zie hiertoe hoofdstuk 4 van deze richtlijn. Ten aanzien van Persoonlijke Verzorging en Begeleiding worden deze</t>
+          <t>Hoofdstuk 2 Toegang, melding en onderzoek &gt; Artikel 6. Gesprek en Vraagverheldering &gt; lid 4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Het College onderzoekt in het gesprek hoe de gewenste samenhang in de versterking van de draagkracht en beperking van de draaglast tot stand kan komen door mede te kijken naar mogelijkheden die lokale voorzieningen bieden op het terrein van welzijn, sport en bewegen, cultuur, onderwijs, vrijwilliger</t>
         </is>
       </c>
     </row>
@@ -1139,19 +1167,20 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>GM1992</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4. Visie sociaal domein Voorne aan Zee &gt; Visie en Missie</t>
+          <t>Aalten</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>We geloven in de kracht van onze inwoners. We vertrouwen erop dat zij, met de draagkracht die ze hebben, de regie over hun eigen leven kunnen voeren. Wanneer er problemen zijn kunnen familie, vrienden of bekenden in eerste instantie helpen om een oplossing te vinden. Als gemeente ondersteunen en mot</t>
+          <t>Beleidsregels mantelzorg en bovengebruikelijke zorg &gt; Artikel</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Mantelzorg wordt in de Wmo 2015 gedefinieerd als “hulp ten behoeve van zelfredzaamheid, participatie, beschermd wonen, opvang, jeugdhulp, het opvoeden en opgroeien van jeugdigen en zorg en overige diensten als bedoeld in de Zorgverzekeringswet die rechtstreeks voortvloeit uit een tussen personen bes</t>
         </is>
       </c>
     </row>
@@ -1161,19 +1190,20 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>GM0785</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Artikel 10: Draagkracht berekening bij aanvraag bijzondere bijstand &gt; lid 6</t>
+          <t>Bronckhorst</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Voor kostensoorten die gerekend moeten worden tot de algemeen noodzakelijke bestaanskosten, maar waarvoor onder bepaalde (individuele) voorwaarden bijzondere bijstand verstrekt kan worden, bedraagt de draagkracht 100% van al het inkomen boven de van toepassing zijnde bijstandsnorm. Dit geldt in iede</t>
+          <t>7. Inkomen en schulden &gt; 7.3 Bijzondere bijstand</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Het gaat bij de verstrekking van bijzondere bijstand om bijstand die wordt verstrekt indien bijzondere omstandigheden in het individuele geval leiden tot noodzakelijke kosten van het bestaan, waarin het inkomen niet voorziet, die niet gedekt kunnen worden door een voorliggende voorziening en die nie</t>
         </is>
       </c>
     </row>
@@ -1184,35 +1214,35 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C17" t="n">
-        <v>1079</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>artikel=699; bijlage=256; toelichting_artikel=54; toelichting_algemeen=22; aanhef=18; begrippen=18; bijlage_pdf=11; ondertekening=1</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>jeugd=579; wmo=368; beide=121; onbekend=11</t>
-        </is>
+        <v>1100</v>
+      </c>
+      <c r="D17" t="n">
+        <v>141</v>
+      </c>
+      <c r="E17" t="n">
+        <v>277</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GM1961</t>
+          <t>jeugd=547; kern=496; aanbod=26; twijfel=25; buiten_scope=6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 4</t>
+          <t>Ermelo</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>De ondersteuning bij persoonlijk functioneren, gezondheid en welzijn zijn taken die in een relatie gedurende alle tijd dat twee mensen samen zijn gewoon meegenomen kan worden en in basis gebruikelijk.
-Soms zijn huisgenoten niet bereid elkaar gebruikelijke hulp te verlenen. Het college onderzoekt dan</t>
+          <t>Hoofdstuk 4. Inzet persoonsgebonden budget voor niet-professionals &gt; Artikel 5 lid 4 van de verordening Jeugdhulp</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>De draaglast en draagkracht van inwoners verschillen. In het gesprek met de klant moet bekeken worden wat het sociaal netwerk redelijkerwijs kan doen. Er moet zodanig maatwerk geboden worden dat de betrokkene de zorg kan volhouden. Niettemin zijn er een aantal toets-elementen aan de hand waarvan een</t>
         </is>
       </c>
     </row>
@@ -1222,20 +1252,22 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>GM0059</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Artikel 4.3. Onderzoek naar de behoeften, persoonskenmerken en voorkeuren &gt; lid 1</t>
+          <t>Westerwolde</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Het Team Jeugd vergaart voldoende kennis over de voor het nemen van een besluit over jeugdhulp van belang zijnde feiten en af te wegen belangen. Het Team Jeugd onderzoekt in samenspraak met de jeugdige, ouder(s) en/of dan wel diens wettelijk vertegenwoordiger:
-a. Wat de hulpvraag van de jeugdige, ou</t>
+          <t>Hoofdstuk 2 Uitgangspunten Wmo 2015 &gt; 2.2 Algemeen afwegingskader &gt; Artikel 2.2.1 Eigen Kracht &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Zelf oplossen
+De gemeente stimuleert de burger zelf regie te voeren en zijn of haar eigen mogelijkheden te benutten. Daarvoor kijkt de Wmo-consulent naar de persoonlijke eigenschappen van de cliënt, zijn talenten en vaardigheden, zingeving, in combinatie met zijn directe omgeving.
+Gebruikelijke hulp</t>
         </is>
       </c>
     </row>
@@ -1245,19 +1277,20 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>GM0222</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 3</t>
+          <t>Hoogeveen</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Naast de aard en ernst van de overbelasting onderzoekt de buurtcoach/jeugd- en gezinswerker of deze komt doordat er iets met de ondersteuner zelf aan de hand is (draagkracht vermindering) en/of dat deze gevolg is van de situatie, bijvoorbeeld van langdurige ziekte van kind of partner (draaglast verh</t>
+          <t>Leefeenheid met kinderen die extra zorg behoeven &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Bij het beoordelen van de extra draaglast van ouders met een kind met een handicap, chronische ziekte of andere beperkingen in het functioneren, wordt gekeken naar wat een kind zonder die beperkingen in vergelijkbare omstandigheden aan zorg nodig zou hebben. Daar waar de gebruikelijke zorg van ouder</t>
         </is>
       </c>
     </row>
@@ -1267,19 +1300,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>GM1729</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hoofdstuk 4: Eigen kracht &gt; Artikel 4.2 Draagkracht en draaglast &gt; lid 4</t>
+          <t>Smallingerland</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>In kortdurende situaties neemt de gemeente aan dat draagkracht en draaglast in balans zijn en bieden ouder(s) eventueel met behulp van het sociale netwerk alle vormen van hulp op het gebied van persoonlijke verzorging, begeleiding en verblijf zelf, tenzij dit gezien de aard van de benodigde hulp (ge</t>
+          <t>Hoofdstuk 2 Melding, onderzoek, aanvraag en beschikking &gt; Artikel 3 Onderzoek naar de ondersteuningsbehoefte &gt; lid 4 &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Draagkracht en draaglast
+a. Een gezonde draagkracht betekent onder meer dat huisgenoten onderling zorg kunnen dragen voor gebruikelijke hulp. Voor zover het van toepassing is en tot de mogelijkheden behoort dat huisgenoten zelf hulp op het gebied van persoonlijke verzorging, begeleiding, vervoer en </t>
         </is>
       </c>
     </row>
@@ -1289,21 +1324,20 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>GM0637</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bijlage &gt; 2. Kan de cliënt rekenen op hulp van familieleden of vrienden die niet tot het huishouden behoren? | Nee |</t>
+          <t>Montferland</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4. Heeft de verzorger als werknemer zorgverlof kunnen opnemen? | Nee, waarom niet?; Ja, hoe lang en hoeveel uren per week?
- | Belasting van mantelzorg
-1. Welke taken worden door de verzorger als (emotioneel en/of fysiek) belastend ervaren? | Hulp bij dagelijkse bezigheden; Persoonlijke verzorging Hu</t>
+          <t>Draagkracht/draaglast mantelzorger</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">De belangen en de draagkracht/draaglast van de mantelzorger worden altijd meegewogen bij het gesprek met de cliënt. Inzet van respijtzorg kan de draagkracht van de mantelzorger versterken. In geval de mantelzorger persoonlijke verzorging (zoals bedoeld in de Zvw) biedt, kan het college bespreekbaar </t>
         </is>
       </c>
     </row>
@@ -1317,32 +1351,33 @@
         <v>330</v>
       </c>
       <c r="C22" t="n">
-        <v>1921</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>artikel=1441; bijlage=314; toelichting_artikel=94; toelichting_algemeen=28; aanhef=24; ondertekening=11; bijlage_pdf=6; begrippen=3</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>jeugd=879; wmo=845; beide=191; onbekend=6</t>
-        </is>
+        <v>1927</v>
+      </c>
+      <c r="D22" t="n">
+        <v>257</v>
+      </c>
+      <c r="E22" t="n">
+        <v>773</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GM1771</t>
+          <t>kern=1139; jeugd=778; twijfel=8; aanbod=2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hoofdstuk 2. Afspraken tussen inwoner en gemeente &gt; Artikel 5. Voorwaarden voor een maatwerkvoorziening &gt; lid 5.1 &gt; 2. Onder eigen kracht en het probleemoplossend vermogen van de inwoner wordt in ieder geval verstaan:</t>
+          <t>Geertruidenberg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>iii. Bij een aanvraag voor een maatwerkvoorziening tot jeugdhulp bekijkt het college wat wordt gedaan om die spanningen te verminderen.
-iv. Als de (dreigende) overbelasting kan worden verminderd door het herinrichten van het werk of andere sociale/maatschappelijke activiteiten wordt dit eerst van de</t>
+          <t>Hoofdstuk 1 Kernbegrippen rond maatschappelijke ondersteuning, voorwaarden en criteria voor een maatwerkvoorziening &gt; 1.4. Gebruikelijke hulp</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>• voor zover een partner, kind en/of andere huisgenoot overbelast is of dreigt te raken wordt van hem of haar geen gebruikelijke hulp verwacht, totdat deze dreigende overbelasting is opgeheven. Daarbij geldt het volgende:
+a. Wanneer voor de partner, ouder, kind en/of andere huisgenoot eigen mogelijk</t>
         </is>
       </c>
     </row>
@@ -1352,19 +1387,23 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>GM0344</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bijlage &gt; Ad D Draagkracht en draaglast</t>
+          <t>Haarlemmermeer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Soms is het zorgen voor een kind, al dan niet in combinatie met andere factoren in het leven van ouder(s), zo zwaar dat sprake is van overbelasting van ouder(s). Er is dan geen of beperkt evenwicht meer tussen draagkracht (=belastbaarheid) en draaglast (=belasting), vaak gekenmerkt door fysieke en/o</t>
+          <t>HOOFDSTUK 1 GEZAMENLIJKE BEPALINGEN VOOR JEUGDWET, WET MAATSCHAPPELIJKE ONDERSTEUNING 2015 EN PARTICIPATIEWET &gt; Artikel 6a. Beoordeling eigen mogelijkheden en probleemoplossend vermogen &gt; lid 3</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Uit het onderzoek kan evenwel blijken dat de eigen mogelijkheden en het probleemoplossend vermogen tekortschiet, omdat sprake is van:
+a. geobjectiveerde beperkingen om noodzakelijke hulp te bieden;
+b. een gebrek aan kennis of vaardigheden om noodzakelijke hulp te bieden; of
+c. overbelasting of dreig</t>
         </is>
       </c>
     </row>
@@ -1374,19 +1413,20 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>GM0579</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hoofdstuk 5 – Voorwaarden individuele voorzieningen jeugdhulp &gt; Artikel 5.2 Beoordeling (boven) gebruikelijke hulp en eigen kracht &gt; lid 5</t>
+          <t>Wijdemeren</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Als er sprake is van gebruikelijke hulp verstrekt het college geen individuele voorziening tot jeugdhulp. Hierop kan (tijdelijk) een uitzondering worden gemaakt als de ouders door (dreigende) overbelasting de gebruikelijke hulp niet kunnen bieden. Er moet dan wel een verband zijn tussen de (dreigend</t>
+          <t>Hoofdstuk 9: Begeleiding, Behandeling en kortdurend verblijf &gt; 9.7. Kortdurend verblijf of respijtzorg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Bij kortdurend verblijf logeert een inwoner in een instelling. Bijvoorbeeld in een gehandicapteninstelling, verpleeghuis of verzorgingshuis. Hierdoor wordt de mantelzorg ontlast, zodat deze de zorg langer kan volhouden en de inwoner thuis kan blijven wonen. Kortdurend verblijf is bedoeld voor mensen</t>
         </is>
       </c>
     </row>
@@ -1396,20 +1436,20 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>GM1982</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hoofdstuk 3. Individuele voorzieningen &gt; Paragraaf 2. Toegang procedureel &gt; Artikel 6. Criteria individuele voorzieningen (eigen kracht) &gt; deel 4</t>
+          <t>Nunspeet</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>d. Wanneer de overbelasting door bijvoorbeeld het herinrichten van het huiselijk leven en/of werk kan worden verminderd, dan wordt dit ook van een ouder verwacht. Het kan dan gaan om zowel een tijdelijke herinrichting als een structurele herinrichting.
-e. Er kan voor gekozen worden een indicatie toe</t>
+          <t>Hoofdstuk 1 Afwegingskader &gt; Artikel 1.8 Afwegingskader &gt; lid 5 &gt; 1.8.3 Andere wetgeving</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Een maatwerkvoorziening kan door het college worden toegekend in natura of in de vorm van een persoonsgebonden budget. Het college houdt rekening met de belangen van mantelzorgers. Zo kan in geval van (een dreigende) overbelasting van de mantelzorger een voorziening aan de inwoner met een beperking </t>
         </is>
       </c>
     </row>
@@ -1419,22 +1459,24 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>GM1658</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 2</t>
+          <t>Raalte</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>○ Begeleiding naar het ziekenhuis (ook meerdere malen per week).
-○ Begeleiding naar zwemles of culturele- en sportverenigingen.
-- Het bieden van een beschermende woonomgeving van ouders aan kinderen is tot een leeftijd van 18 jaar gebruikelijke hulp, zowel in kortdurende als langdurige situaties.
-Ui</t>
+          <t>Hoofdstuk 4. Gezond en veilig opgroeien &gt; Artikel 4.5 Beoordeling eigen mogelijkheden en probleemoplossend vermogen &gt; lid 4</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Slechts indien uit het onderzoek blijkt dat deze mogelijkheden ontoereikend zijn vanwege:
+a. geobjectiveerde beperkingen bij de ouder(s) of de jeugdige;
+b. een aantoonbaar gebrek aan kennis of vaardigheden om noodzakelijke hulp te bieden; of
+c. (dreigende) overbelasting van de ouder(s),
+kan de gemee</t>
         </is>
       </c>
     </row>
@@ -1448,32 +1490,32 @@
         <v>342</v>
       </c>
       <c r="C27" t="n">
-        <v>5830</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>artikel=4035; bijlage=741; toelichting_artikel=670; toelichting_algemeen=191; begrippen=76; aanhef=72; bijlage_pdf=29; ondertekening=16</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>wmo=3136; jeugd=2253; beide=412; onbekend=29</t>
-        </is>
+        <v>5847</v>
+      </c>
+      <c r="D27" t="n">
+        <v>296</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1652</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GM1924</t>
+          <t>kern=2247; jeugd=2014; buiten_scope=828; twijfel=581; aanbod=175; waardering=2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Toelichting &gt; Algemeen &gt; Begrip inkomsten kunnen verwerven</t>
+          <t>Nieuwegein</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Gelet op de toelichting bij artikel 36b Participatiewet wordt hier bedoeld in het geheel geen inkomen te verwerven. Beoordeeld moet worden of een student met een structurele medische beperking al dan niet voldoende kan werken zonder dat dit ten koste gaat van de studie.
-Burgemeester en wethouders mo</t>
+          <t>2. Uitwerking pijlers &gt; 2.3 Toeleiding naar passende ondersteuning</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Nieuwegein heeft het sociaal team Geynwijs een belangrijke rol in de toeleiding naar passende ondersteuning voor inwoners met een ondersteuningsvraag. Bij problemen op uiteenlopende levensgebieden, van psychische klachten, gevoelens van eenzaamheid, tot lichamelijke beperkingen die het dagelijks </t>
         </is>
       </c>
     </row>
@@ -1483,19 +1525,24 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>GM0160</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hoofdstuk 3: Onderzoek en opstellen ondersteuningsplan &gt; 3.3 Oplossingsmogelijkheden toegelicht &gt; Artikel 3.3.2 Gebruikelijke hulp</t>
+          <t>Altena</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bij de beoordeling van maatschappelijke ondersteuning onderzoekt Samen Doen of gebruikelijke hulp mogelijk is. Dit is hulp die in redelijkheid verwacht mag worden van huisgenoten zoals een partner, ouder of kind. Het uitgangspunt is dat leden van een huishouden elkaar ondersteunen bij dagelijkse tak</t>
+          <t>2 De hulpvraag &gt; Artikel 2.7 Uitzonderingen &gt; lid 2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2. De gemeente maakt afspraken met de huisartsen, de medisch specialisten, de jeugdartsen en de zorgverzekeraars over zulke doorverwijzingen. De gemeente stemt met de gecertificeerde instelling of jeugdreclassering vindt af.
+2.7.2
+Spoedeisende gevallen
+JEUGDWET|WMO|PW|LLV|WGS
+In spoedeisende gevalle</t>
         </is>
       </c>
     </row>
@@ -1505,19 +1552,35 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>GM0160</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hoofdstuk 1: Algemene uitgangspunten &gt; 1.2 Toegang via Samen Doen &gt; Artikel</t>
+          <t>Berkelland</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Jeugdigen en/of ouders kunnen een hulpvraag melden bij het sociaal wijkteam. Samen Doen Hardenberg BV is de organisatie die als sociaal wijkteam het college adviseert over de toegang tot Wmo en Jeugdhulp en integrale ondersteuning biedt aan de inwoners. Samen Doen helpt inwoners met vragen over wone</t>
+          <t>4 Gezond en veilig opgroeien &gt; 4.1 Uitgangspunten &gt; Artikel 4.2 Vrij toegankelijke hulp &gt; lid 1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. De
+gemeente
+zet zich ervoor in dat
+jongeren
+zoveel mogelijk gezond, kansrijk en veilig kunnen opgroeien. Om dat te bereiken biedt de
+gemeente
+hulp
+aan die vrij toegankelijk is. De
+inwoner
+kan van deze
+hulp
+gebruik maken, zonder besluit van de
+gemeente
+. Ook heeft de
+inwoner
+geen verwijzing nodig </t>
         </is>
       </c>
     </row>
@@ -1527,19 +1590,22 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>GM1892</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Toelichting &gt; Artikel 6 &gt; Afzien medisch advies</t>
+          <t>Blaricum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Artikel 36b lid 2 Participatiewet biedt de mogelijkheid om af te zien van een medisch advies. Het college kan dit doen op grond van bij het college bekende gegevens of door de belanghebbende verstrekte gegevens. Dit kan alleen als op voorhand duidelijk is dat er recht bestaat op een studietoeslag. W</t>
+          <t>Hoofdstuk 3 Algemene voorziening en voorliggende oplossingen &gt; Artikel 3.1.7 Andere vormen van gebruikelijke hulp</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ook bij andere gezamenlijke huishoudens (bijvoorbeeld ouders met volwassen kinderen of andere volwassen huisgenoten) is er vaak sprake van gebruikelijke hulp. Denk aan:
+• begeleiding bij deelname in de maatschappij.
+• begeleiding bij sociaal contact, zoals het bezoeken van familie of naar de huisart</t>
         </is>
       </c>
     </row>
@@ -1549,22 +1615,23 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>GM0823</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2. Lokale visie op gezondheid &gt; 2.1 Onze uitgangspunten &gt; deel 1</t>
+          <t>Zwartewaterland</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>In het afgeleide van de landelijke visie en de leidende principes uit onze Strategische visie op de sociale leefomgeving gaan we bij het lokaal gezondheidsbeleid 2022-2026:
-a.
-daadwerkelijk werken vanuit het concept van positieve gezondheid
-Gemeente Oirschot wil de bewustwording over de kansrijke mo</t>
+          <t>Hoofdstuk 12 Begrippenlijst &gt; Artikel &gt; deel 11</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Uitkering:
+de bijstandsuitkering, de IOAW- of de IOAZ-uitkering.
+Uitkeringsnorm:
+de maximale hoogte van een uitkering in de persoonlijke situatie van de inwoner; dit is de toepasselijke bijstandsnorm uit de Participatiewet of de grondslag bedoeld in de IOAW of IOAZ. Gaat het om een jongere van 18 to</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1590,35 +1657,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_gemeenten</t>
+          <t>n_gemeenten_corpus</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>n_passages</t>
+          <t>n_passages_corpus</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sectietype_verdeling</t>
+          <t>n_gemeenten_filter</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>domein_verdeling</t>
+          <t>n_passages_filter</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>categorie_verdeling (heel corpus)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>voorbeeld_gemeente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>voorbeeld_pad</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>voorbeeld_tekst</t>
         </is>
@@ -1634,32 +1706,33 @@
         <v>243</v>
       </c>
       <c r="C2" t="n">
-        <v>410</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>artikel=360; toelichting_artikel=20; bijlage=16; toelichting_algemeen=9; aanhef=3; bijlage_pdf=2</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>wmo=366; beide=35; jeugd=7; onbekend=2</t>
-        </is>
+        <v>411</v>
+      </c>
+      <c r="D2" t="n">
+        <v>232</v>
+      </c>
+      <c r="E2" t="n">
+        <v>369</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GM0297</t>
+          <t>kern=390; buiten_scope=12; jeugd=6; waardering=1; aanbod=1; twijfel=1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aanhef</t>
+          <t>Kapelle</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Intitulé
-Het is belangrijk dat mensen zo lang mogelijk zelfstandig thuis kunnen blijven wonen. Dit geldt zowel voor ouderen die een toenemende kans hebben op lichamelijke beperkingen of cognitieve achteruitgang (zoals dementie), als voor als voor jongere inwoners met een chronische lichamelijke, ver</t>
+          <t>Artikel 4. Onderzoek naar de behoeften, persoonskenmerken en voorkeuren &gt; lid 1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Het college onderzoekt in samenspraak met degene door of namens wie de melding is gedaan en waar mogelijk met de mantelzorger of mantelzorgers dan wel zijn vertegenwoordiger en desgewenst familie, zo spoedig mogelijk, doch uiterlijk binnen zes weken na ontvangst van de melding:
+a. de behoeften, pers</t>
         </is>
       </c>
     </row>
@@ -1669,20 +1742,20 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>GM0177</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1. Het proces van melding tot beschikking &gt; 1.1. Beschermd Wonen en Beschut Wonen &gt; deel 2</t>
+          <t>Renswoude</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>• de behoefte aan maatregelen ter ondersteuning van de mantelzorger van de cliënt;
-• de mogelijkheden om met gebruikmaking van een algemene voorziening of door het verrichten van maatschappelijk nuttige activiteiten te komen tot verbetering van zijn zelfredzaamheid of zijn participatie, onderscheide</t>
+          <t>Hoofdstuk 9. Respijtzorg - vervangende mantelzorg &gt; Artikel 20 - Respijtzorg – Kortdurend Verblijf &gt; lid 1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1. Respijtzorg-vervangende mantelzorg kan als een tijdelijke ondersteuning van de mantelzorger of van de cliënt worden toegekend.</t>
         </is>
       </c>
     </row>
@@ -1692,19 +1765,21 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>GM0269</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HOOFDSTUK 2: Melding, onderzoek en aanvraag &gt; Artikel 5. Gesprek &gt; lid 1</t>
+          <t>Drimmelen</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Het college of de hiervoor in artikel 2 lid 3 bedoelde instantie onderzoekt in een gesprek tussen deskundigen en degene door of namens wie de melding is gedaan, dan wel diens vertegenwoordiger en waar mogelijk met de mantelzorger of mantelzorgers, cliëntondersteuners en desgewenst familie of persone</t>
+          <t>Hoofdstuk 1 Procedureregels aanvraag maatschappelijke ondersteuning &gt; Artikel 4. Gesprek &gt; lid 1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Het college onderzoekt in een gesprek tussen deskundigen en de degene door of namens wie de melding is gedaan, dan wel diens vertegenwoordiger en waar mogelijk met de mantelzorger of mantelzorgers en desgewenst familie, zo spoedig mogelijk en voor zover nodig:
+a. de behoeften, persoonskenmerken en v</t>
         </is>
       </c>
     </row>
@@ -1714,20 +1789,22 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>GM0362</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Artikel 5 Gesprek &gt; lid 1</t>
+          <t>Houten</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Het college onderzoekt in een gesprek tussen deskundigen en de degene door of namens wie de melding is gedaan, dan wel diens vertegenwoordiger en waar mogelijk met de mantelzorger of matelzorgers en desgewenst familie, zo spoedig mogelijk na de melding en voor zover nodig:
-a. de hulpvraag van de </t>
+          <t>Toelichting &gt; Artikel 2.3 &gt; Zesde lid – verrichten van het onderzoek</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Om een goed beeld te krijgen van de inwoner, diens persoonlijke situatie en de hulpvraag, is een uitgebreid en zorgvuldig onderzoek nodig. De door het college gemandateerde professional voert het onderzoek uit namens het college en volgt hierin een aantal verplichte stappen
+1
+Deze stappen volgen uit</t>
         </is>
       </c>
     </row>
@@ -1737,20 +1814,22 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>GM0377</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hoofdstuk 2 Melding en Onderzoek &gt; Artikel 3 Onderzoek naar behoeften, persoonskenmerken en voorkeuren &gt; lid 1</t>
+          <t>Epe</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Het college onderzoekt in een gesprek met de cliënt of degene die de melding namens de cliënt heeft gedaan, dan wel de vertegenwoordiger van de cliënt en waar mogelijk de mantelzorger(s) en desgewenst de familie, uiterlijk binnen zes weken na ontvangst van de melding en voor zover nodig:
-a. de behoe</t>
+          <t>Hoofdstuk 2: Melding, onderzoek en aanvraag &gt; Artikel 2.4 Gesprek &gt; lid 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Bij het onderzoek wordt conform lid 1 het volgende meegewogen:
+a. welke hulp passend is bij de behoeften, persoonskenmerken en voorkeuren van de inwoner;
+b. de mogelijkheden op eigen kracht of met gebruikelijke hulp zijn/haar zelfredzaamheid of participatie te handhaven of te verbeteren of te voorzi</t>
         </is>
       </c>
     </row>
@@ -1764,31 +1843,32 @@
         <v>322</v>
       </c>
       <c r="C7" t="n">
-        <v>1992</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>artikel=1465; bijlage=350; toelichting_artikel=55; begrippen=35; aanhef=32; toelichting_algemeen=30; bijlage_pdf=15; ondertekening=10</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>wmo=1385; jeugd=449; beide=143; onbekend=15</t>
-        </is>
+        <v>2000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>285</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1094</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GM0473</t>
+          <t>kern=1410; jeugd=399; aanbod=126; twijfel=59; buiten_scope=5; waardering=1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Artikel 6 Residentiële hulp in de vorm van respijtzorg (artikel 3.4 verordening) &gt; lid 1</t>
+          <t>Wageningen</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Een individuele voorziening in de vorm van respijtzorg (kortdurend verblijf) wordt ingezet indien de respijtzorg een onderdeel is van een bredere jeugdhulpinzet.</t>
+          <t>10. Zorg voor de zorger: ondersteunen van mantelzorg &gt; deel 6</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10-e | Behoeften van mantelzorgers aan onder andere praktische hulp en respijtzorg, financiële tegemoetkoming/materiële hulp (bijlage II-F) | Mantelzorgers worden betrokken bij het aanvragen van Wmo-voorzieningen door hun zorgvrager | Overbelasting van mantelzorgers wordt zichtbaar en kan worden voo</t>
         </is>
       </c>
     </row>
@@ -1798,20 +1878,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>GM0893</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6. Logeren &gt; Artikel 6.1 Inleiding</t>
+          <t>Valkenswaard</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Logeren is een vorm van begeleiding die wordt ingezet om de mantelzorger(s) en de directe
-omgeving tijdelijk te ontlasten, met als resultaat het versterken en/of behoud van de mantelzorg en een leefbare thuissituatie. Logeren is een voorziening die bedoeld is als respijtvoorziening. Dat houdt in dit</t>
+          <t>Hoofdstuk 1 Begripsomschrijvingen &gt; deel 4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Lid 16. Respijtzorg: Respijtzorg is de tijdelijke en volledige overname van de zorg van een mantelzorger met het doel om die mantelzorger vrijaf te geven.
+Lid 17. Voorziening in natura: Een voorziening, in te zetten om het resultaat te bereiken, in de vorm van goederen in lease of in eigendom, of al</t>
         </is>
       </c>
     </row>
@@ -1821,21 +1902,20 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>GM0344</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hoofdstuk 6. Weging specifieke maatwerkvoorzieningen &gt; 6.9 Leidraad kortdurend verblijf &gt; Artikel 6.9.1 Kortdurend verblijf ter ontlasting van de mantelzorger (A) &gt; lid 5</t>
+          <t>Sittard-Geleen</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5. De persoon voor wie de mantelzorger de verantwoordelijkheid draagt is aangewezen op zorg die gepaard gaat met toezicht op regelmatige en onregelmatige momenten.
-6.9.1.2 Omvang
-Omdat kortdurend verblijf gericht is op het respijt bieden aan de mantelzorger wordt deze toegekend voor maximaal 36 etma</t>
+          <t>Hoofdstuk 9 Kortdurend verblijf &gt; 9.1 Inleiding</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>De gemeente is verantwoordelijk voor respijtzorg. Respijtzorg is een tijdelijke en volledige overname van ondersteuning met als doel de mantelzorger een adempauze te geven. Respijtzorg is een vorm van ondersteuning van de mantelzorger. Door af en toe vrij te zijn van mantelzorgtaken, kunnen mantelzo</t>
         </is>
       </c>
     </row>
@@ -1845,19 +1925,20 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>GM0512</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Toelichting &gt; Artikel 1.2 &gt; Artikel 1.2 Doelgroep van de verordening</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>De verordening kent twee doelgroepen. Ten eerste ingezetenen die ondersteuning nodig hebben vanwege een of meer beperkingen en/of chronische psychische of psychosociale problemen bij het versterken van hun zelfredzaamheid en behoud van participatie. Als ingezetenen worden ook gezien: personen die hu</t>
+          <t>Hoofdstuk 9 – Kortdurend verblijf (respijtzorg) &gt; Preventieve werking</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Kortdurend verblijf betreft dus een ondersteuningsvorm met als doel het overnemen van de zorg ter ontlasting van de gebruikelijke hulp of de mantelzorger(s). Deze vorm van ondersteuning is een noodzaak om de zorg vol te kunnen houden. Kortdurend verblijf heeft dan ook een belangrijk preventief effec</t>
         </is>
       </c>
     </row>
@@ -1867,19 +1948,20 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>GM0547</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hoofdstuk 9. Overige bepalingen &gt; Artikel 9.1.3. Maatwerkvoorziening kortdurend verblijf</t>
+          <t>Venray</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kortdurend verblijf is een vorm van respijtzorg. Het zwaartepunt ligt vooral op logeren, met als doel het overnemen van het (permanente) toezicht ter ontlasting van de persoon die de gebruikelijke hulp geeft of de mantelzorger. Er is geen sprake van (medische) opname in het kader van de Zorgverzeker</t>
+          <t>8 De vorm van de hulp &gt; 8.3 Persoonsgebonden budget (pgb) &gt; Artikel 8.3.3 Hoogte en tarief pgb &gt; lid 6</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Voor respijtzorg uitgevoerd door niet-professionele hulp bestaat ook een tegemoetkoming per kalendermaand zoals genoemd in het besluit nadere regels.</t>
         </is>
       </c>
     </row>
@@ -1893,34 +1975,32 @@
         <v>302</v>
       </c>
       <c r="C12" t="n">
-        <v>1330</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>artikel=939; bijlage=288; toelichting_artikel=54; aanhef=15; toelichting_algemeen=12; bijlage_pdf=12; begrippen=8; ondertekening=2</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>wmo=923; jeugd=292; beide=103; onbekend=12</t>
-        </is>
+        <v>1331</v>
+      </c>
+      <c r="D12" t="n">
+        <v>234</v>
+      </c>
+      <c r="E12" t="n">
+        <v>748</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GM1711</t>
+          <t>kern=1001; jeugd=260; twijfel=35; buiten_scope=23; aanbod=12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bijlage &gt; 3. Overnemen</t>
+          <t>Teylingen</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wanneer er (in uitzonderingsgevallen) voor een cliënt één dagdeel per dag is geïndiceerd, moet de aanbieder voor deze cliënt het vervoer organiseren.
-Begeleiding groep vindt bij voorkeur plaats in de nabijheid van de woon- of verblijfsplaats van de cliënt.
-Kortdurend verblijf
-Kortdurend verblijf is </t>
+          <t>HOOFDSTUK 3 BEOORDELING VAN DE AANSPRAAK &gt; 3.15 Kortdurend Verblijf / Respijtzorg &gt; deel 2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>De aanvrager is zelf verantwoordelijk voor vervoer van en naar de instelling voor kortdurend verblijf. Een aanvrager die is aangewezen op zorg met permanent toezicht en/of 24 uur per dag zorg in de nabijheid komt in aanmerking voor een indicatie voor de Wlz. Een uitzondering hierop geldt wanneer het</t>
         </is>
       </c>
     </row>
@@ -1930,19 +2010,20 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>GM1735</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6. Logeerzorg</t>
+          <t>Moerdijk</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Logeerzorg ter ontlasting van de mantelzorger is mogelijk via de Wmo. De taken van de mantelzorger worden dan tijdelijk overgenomen, zodat de mantelzorger tot rust kan komen of tijd voor zichzelf heeft. Dit kan betekenen dat de cliënt tijdelijk elders in een instelling logeert. De omvang van de loge</t>
+          <t>Hoofdstuk 2 Afwegingskaders om te komen tot een maatwerkoplossing &gt; 2.8 Begeleiding: ontwikkeling, stabilisatie, verminderde zelfredzaamheid en logeerzorg &gt; Artikel 2.8.1. Afwegingskader &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Het gaat om activiteiten gericht op het bevorderen of behoud van de zelfredzaamheid en/of maatschappelijke participatie. Gedacht kan worden aan het kunnen doen van de administratie, het plannen van de week, regelzaken- en geldzaken, het uitvoeren van algemeen dagelijkse levensverrichtingen, het hebb</t>
         </is>
       </c>
     </row>
@@ -1952,19 +2033,21 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>GM0777</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 24</t>
+          <t>Stichtse Vecht</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Doelgroep:; Voor logeerzorg komen cliënten met chronische (complexe) problemen door een somatische, zintuiglijke of verstandelijke beperking, een psychische- of cognitieve aandoening of dementie / geheugenproblemen in aanmerking. Bij de mantelzorger van deze cliënt is ontlasting nodig om (dreigende)</t>
+          <t>4. Regels voor een persoonsgebonden budget (pgb) bij een maatwerkvoorziening &gt; 4.12 Pgb bij individuele begeleiding, dagbesteding en kortdurend verblijf</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Voorwaarden:
+De Wmo stelt dat de cliënt met zijn pgb een gelijkwaardige voorziening moet kunnen treffen. Voor begeleiding, dagbesteding en kortdurend verblijf (logeeropvang)  betekent dit dat er een zorgverlener van betaald moet kunnen worden Eventuele ondersteuning wordt door de SVB voor cliënt gra</t>
         </is>
       </c>
     </row>
@@ -1974,26 +2057,20 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>GM0599</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bijlage &gt; 3. UITGANGSPUNTEN VOOR UITVOERING VAN HET TOEZICHT</t>
+          <t>Lansingerland</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>■ Sociale en arbeidsmatige dagbesteding.
-■ Beschermd wonen.
-■ Overbruggingszorg.
-■ Logeerzorg.
-■ Bemoeizorg.
-■ Respijtzorg.
-■ Maatschappelijke opvang: algemene voorziening, zoals nachtopvang.
-■ Maatschappelijke opvang: maatwerkvoorziening (aan de hand van een indicatie) met reguliere of intensieve b</t>
+          <t>4 Wmo &gt; 4.4 Kortdurend verblijf &gt; Artikel 4.4.1 Wat verstaan we eronder?</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Kortdurend verblijf is bedoeld voor mensen die toezicht nodig hebben. Bijvoorbeeld als er valgevaar is of als de inwoner zelf niet in staat is hulp in te roepen als dat nodig is of omdat er ernstige gedragsproblemen zijn. Het kan ook gaan om constante zorg of zorg op ongeregelde tijdstippen, bijvoor</t>
         </is>
       </c>
     </row>
@@ -2003,20 +2080,21 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>GM0589</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Artikel 11. Begeleiding &gt; lid 4</t>
+          <t>Ouder-Amstel</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4. De mogelijkheden van de specifieke dagbestedingsgroep.
-Er wordt hierbij uitgegaan van de tarieven, zoals die zijn overeengekomen in de contracten voor zorg in natura. De tarieven voor begeleiding zijn te vinden op de volgende website: https://inkooputrechtwest.nl/inkoop/tarieven-en-productcodelij</t>
+          <t>1 Financieel besluit &gt; Artikel 1.6 Prijspeil</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">De bedragen van de forfaitaire tegemoetkomingen kunnen jaarlijks worden geïndexeerd aan de hand van de consumentenprijsindex (CPI).
+De tarieven voor persoonsgebonden budgetten voor Hulp bij het huishouden door een niet professionele ondersteuner komen overeen met 75% van het laagste tarief van deze </t>
         </is>
       </c>
     </row>
@@ -2030,33 +2108,34 @@
         <v>340</v>
       </c>
       <c r="C17" t="n">
-        <v>7514</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>artikel=4922; bijlage=1900; toelichting_artikel=300; toelichting_algemeen=105; aanhef=102; ondertekening=71; bijlage_pdf=63; begrippen=51</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>wmo=5708; jeugd=1169; beide=574; onbekend=63</t>
-        </is>
+        <v>7503</v>
+      </c>
+      <c r="D17" t="n">
+        <v>332</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3670</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GM1963</t>
+          <t>kern=5297; jeugd=1020; twijfel=495; buiten_scope=363; aanbod=328</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bijlage &gt; 5. Kortdurend Verblijf, en</t>
+          <t>Westland</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.2.
-Product Arbeidsmatige Dagbesteding Basis
-Arbeidsmatige Dagbesteding Basis voorziet in een structurele activerende daginvulling. Het activiteitenprogramma van dit product biedt de Cliënt structuur, sociale contacten en zingeving. Bij de activiteiten wordt begeleiding geboden in een groep. Persoo</t>
+          <t>Artikel 10. Pgb tarieven beschermd wonen en maatschappelijke opvang</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Voor het bepalen van de hoogte van een pgb ten behoeve van beschermd wonen of maatschappelijke opvang hanteert het college de volgende tarieven, gebaseerd op de tarieven van de aanbieders:
+Zorgprofiel | Product-code | Grondslag; tarief | Tarief 2025; incl. indexatie | Tarief 2026; incl. indexatie
+Be</t>
         </is>
       </c>
     </row>
@@ -2066,23 +2145,22 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>GM0758</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HOOFDSTUK 2: VORMEN VAN JEUGDHULP &gt; § 2 Individuele voorzieningen &gt; Artikel 2.3 Nadere afbakening van te verlenen individuele voorzieningen &gt; lid 1</t>
+          <t>Oosterhout</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>De volgende individuele voorzieningen hebben in beginsel de volgende maximale duur en frequentie:
-a. Ambulante behandeling:
-- Behandeling individueel: maximaal 80 uur per 12 maanden
-- Dagbehandeling licht: maximaal 250 uur per 6 maanden
-- Dagbehandeling zwaar: maximaal 1665 uur per 12 maanden (leeft</t>
+          <t>Hoofdstuk 4 Maatwerkvoorzieningen &gt; 4.5.5 Resultaatgebieden &gt; 1. Sociaal en persoonlijk functioneren</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5. Dagbesteding, het hebben van een zinvolle dag invulling
+Deze begeleiding is gericht op het hebben van een dagelijkse en wekelijkse structuur waarbij het behouden en/of ontwikkelen van vaardigheden centraal staat.
+Doelen die binnen dit resultaatgebied passen zijn o.a.:; • de inwoner heeft een zinv</t>
         </is>
       </c>
     </row>
@@ -2092,20 +2170,24 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>GM0642</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hoofdstuk 5 Beschermd wonen &gt; Artikel 5.7 Indicatiestelling &gt; lid 4</t>
+          <t>Opsterland</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4. Bij het bepalen van het arrangement en de locatie waar beschermd wonen plaatsvindt, spelen zorginhoudelijke en participatiecriteria een rol. De volgende beoordelingscriteria worden toegepast, in overleg met de cliënt:
-a. Wat is de beste omgeving waarin aan participatie gewerkt kan worden? Hierbij</t>
+          <t>Hoofdstuk 9 – Begeleiding &gt; 9.2.3 Arbeidsmatige dagbesteding</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Resultaten
+Het resultaat van arbeidsmatige dagbesteding bestaat uit:
+een werkplek waarin de capaciteiten van de inwoner optimaal gebruikt en ontwikkeld worden;
+een takenpakket dat passend is bij de (ontwikkelings-)mogelijkheden;
+het leren van praktische vaardigheden ten behoeve van het uitvoeren van</t>
         </is>
       </c>
     </row>
@@ -2115,20 +2197,20 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>GM0505</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bijlage &gt; 4. Arbeidsmatige dagbesteding intensief (AMi)</t>
+          <t>Baarle-Nassau</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bij de arbeidsmatige dagbesteding is er een zware, intensieve variant. Deze intensieve variant is enkel aan de orde indien de cliënt in aanmerking komt voor arbeidsmatige dagbesteding (zie criteria boven) en daarnaast voldoet aan een van de volgende criteria:
-- De cliënt heeft structureel (niet epis</t>
+          <t>Artikel 15. Hoogte pgb &gt; lid 6</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>De hoogte van een pgb voor het vervoer van en naar de dagbesteding is gelijk aan het in de regio gangbare toepasselijke tarief, uitgaande van de dichtst bij de woning van de cliënt gelegen geschikte dagbestedingslocatie en rekening houdende met eventuele beperkingen die het reizen met bepaalde vorme</t>
         </is>
       </c>
     </row>
@@ -2138,19 +2220,22 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>GM1916</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Toelichting &gt; Artikel 13 &gt; Achtste lid</t>
+          <t>Zaanstad</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Met dit lid wordt beoogd het gebruik van individuele begeleiding zorgvuldig en terughoudend toe te passen. Individuele begeleiding is een zwaar en ingrijpend middel, dat alleen wordt ingezet op basis van een vastgesteld afwegingskader. Dit geldt zowel in relatie tot verblijf, onderwijs, dagbesteding</t>
+          <t>Hoofdstuk 4: Afwegingen en criteria bij maatwerkvoorzieningen &gt; Artikel 4.5 Afwegingskader &gt; lid 4</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4. Indien overwogen wordt om het primaat van verhuizing toe te passen zullen een aantal factoren die bij de besluitvorming een rol kunnen spelen, afgewogen moeten worden:
+a. Welke voorzieningen zijn nu nodig en welke voorzieningen zijn er in de toekomst, voorzienbaar, nodig?
+Als verwacht wordt dat v</t>
         </is>
       </c>
     </row>
@@ -2161,35 +2246,36 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C22" t="n">
-        <v>803</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>artikel=627; bijlage=96; aanhef=34; toelichting_artikel=17; toelichting_algemeen=13; bijlage_pdf=11; begrippen=5</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>wmo=668; beide=64; jeugd=60; onbekend=11</t>
-        </is>
+        <v>808</v>
+      </c>
+      <c r="D22" t="n">
+        <v>156</v>
+      </c>
+      <c r="E22" t="n">
+        <v>389</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GM0189</t>
+          <t>kern=477; aanbod=191; twijfel=68; jeugd=44; buiten_scope=16; waardering=12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ALGEMEEN AFWEGINGSKADER &gt; Artikel 3.2.2.4 Factoren die geen reden zijn om van gebruikelijke hulp af te wijken</t>
+          <t>Bergen (L.)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.2.3 Mantelzorg
-Mantelzorg is hulp die een inwoner aan iemand biedt om bij te dragen aan zelfredzaamheid, participatie, beschermd wonen, opvang, jeugdhulp, het opvoeden en opgroeien van jeugdigen of aan zorg zoals bedoeld in de Zorgverzekeringswet. Deze hulp komt voort uit een bestaande sociale rel</t>
+          <t>2. Wettelijk kader en positionering in Bergen &gt; Artikel</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Mantelzorgers lopen het risico overbelast te raken. Dit kan ertoe leiden dat zij zelf ziek worden, moeten stoppen met werken of hun sociale contacten verliezen. We vinden het daarom belangrijk om onze mantelzorgers te ondersteunen.
+Daarnaast ligt er vanuit de Wet maatschappelijke ondersteuning (Wmo;</t>
         </is>
       </c>
     </row>
@@ -2199,27 +2285,20 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>GM0687</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3. Maatschappelijke ondersteuning &gt; Artikel 31. Aanbod van algemene voorzieningen</t>
+          <t>Roosendaal</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Algemene voorzieningen zijn:
-a. inloopvoorzieningen
-b. welzijnswerk
-c. maatschappelijke dienstverlening
-d. sociaal team
-e. slachtofferhulp
-f. onafhankelijke cliëntondersteuning
-g. mantelzorgondersteuning
-h. vrijwilligersondersteuning</t>
+          <t>Artikel 7. Ondersteuning door mantelzorgers en vrijwilligers &gt; deel 2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Vervolgens beoordeelt het college of in het gesprek alle voorliggende voorzieningen zijn meegenomen. Behandeling is een voorliggende voorziening. Alvorens een maatwerkvoorziening op grond van de Wmo te verstrekken is het van belang om na te gaan wat de mogelijkheden van behandeling zijn. Hierbij gel</t>
         </is>
       </c>
     </row>
@@ -2229,19 +2308,20 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>GM0599</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hoofdstuk 3 Individuele voorzieningen jeugdhulp, maatwerkvoorzieningen maatschappelijke ondersteuning, gezinsarrangementen, pgb, verplichtingen en overige maatregelen &gt; Paragraaf 3.2 Maatwerkvoorzieningen Wmo 2015 &gt; Artikel 3.2.14 Aanvullende criteria resultaatgebied mantelzorgondersteuning met verblijf &gt; lid 4</t>
+          <t>Terschelling</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Een cliënt die in aanmerking komt voor ondersteuning binnen het resultaatgebied semimurale ondersteuning, intramurale ondersteuning of verblijf, kan niet in aanmerking komen voor ondersteuning voor het resultaatgebied mantelzorgondersteuning met verblijf.</t>
+          <t>3 Het onderzoek &gt; 3.6 Mantelzorg en hulp van andere personen uit het sociale netwerk &gt; deel 2</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>In het onderzoek bekijkt de gemeente of de inwoner mantelzorg ontvangt. In het (keukentafel)gesprek kan de gemeente de inwoner vragen om in zijn netwerk te vragen of iemand mantelzorg wil bieden. Ontvangt een inwoner mantelzorg, dan bekijkt de gemeente in het gesprek hoe de (fysieke) gesteldheid van</t>
         </is>
       </c>
     </row>
@@ -2251,20 +2331,26 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>GM0995</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4.3 Huidige lokale inzet &gt; 2. Activerende huisbezoeken (LPPO</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>• ondersteunen van mantelzorgers uit het Caribische gebied; de verwachting is dat de vraag vanuit deze hoek in de komende tijd aanzienlijk toe zal nemen; Kosten ureninzet: € 17.490, in 2009 zal dit worden ingebouwd in het reguliere aanbod;
-• aanbieden van een gratis Mezzo-jaarlidmaatschap aan mantel</t>
+          <t>Hoofdstuk 3 Individuele voorzieningen jeugdhulp, maatwerkvoorzieningen maatschappelijke ondersteuning, gezinsarrangementen, pgb, verplichtingen en overige maatregelen &gt; Paragraaf 3.2 Maatwerkvoorzieningen Wmo 2015 &gt; Artikel 3.2.1 Maatschappelijke Ondersteuning binnen resultaatgebieden &gt; lid 1</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maatschappelijke ondersteuning in de vorm van dienstverlening vindt plaats in de vorm van één of meer van de volgende resultaatgebieden:
+a. sociaal en persoonlijk functioneren;
+b. huishoudelijke ondersteuning;
+c. financiën;
+d. dagbesteding;
+e. ondersteuning bij zelfzorg en gezondheid;
+f. semimurale </t>
         </is>
       </c>
     </row>
@@ -2274,19 +2360,20 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>GM1926</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3. Lokale Inclusie Agenda &gt; 3.8 Welzijn, ondersteuning en gezondheid &gt; deel 2</t>
+          <t>Capelle aan den IJssel</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verder zijn er onafhankelijke cliëntondersteuners die de toegankelijkheid van het aanvragen van voorzieningen vergroten. Voorafgaand aan het aanvragen van voorzieningen worden inwoners gewezen op de mogelijkheid om gebruik te maken van een cliëntondersteuner. De cliëntondersteuner is kosteloos voor </t>
+          <t>3 Procedure &gt; 3.6 Inzet eigen mogelijkheden/eigen kracht bepalen &gt; 4. Het verlenen van mantelzorg is nooit afdwingbaar;</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>De noodzaak van de mantelzorgondersteuning is veelal gelegen in het gegeven dat mantelzorg zo veel beslag op iemands eigen daginvulling kan leggen dat er geen tijd meer overblijft voor een eigen "leven" waardoor de mantelzorger met zijn of haar vele mantelzorgactiviteiten en de onmogelijkheid weg te</t>
         </is>
       </c>
     </row>
@@ -2302,31 +2389,30 @@
       <c r="C27" t="n">
         <v>600</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>artikel=455; bijlage=92; bijlage_pdf=21; toelichting_artikel=15; toelichting_algemeen=10; aanhef=5; begrippen=2</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>wmo=524; jeugd=31; beide=24; onbekend=21</t>
-        </is>
+      <c r="D27" t="n">
+        <v>111</v>
+      </c>
+      <c r="E27" t="n">
+        <v>310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GM0189</t>
+          <t>kern=370; twijfel=111; aanbod=76; jeugd=26; waardering=9; buiten_scope=8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4.6.3 Toegang regionaal &gt; deel 1</t>
+          <t>Westland</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Het advies- en meldpunt voor huiselijk geweld en kindermishandeling (AMHK)
-Dit wordt wettelijk verankerd in de nieuwe Wmo. Het AMHK wordt gevormd door een samengaan van het huidige Advies- en Meldpunt Kindermishandeling (AMK) en het Steunpunt Huiselijk Geweld (SHG). Het AMHK:
-- zal fungeren als herk</t>
+          <t>HOOFDSTUK 7 OVERIGE BEPALINGEN &gt; Artikel 20. Blijk van waardering mantelzorgers &gt; lid 1</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Mantelzorgers van cliënten in de gemeente Westland kunnen door middel van een melding bij het mantelzorgsteunpunt van Vitis Welzijn voor het ontvangen van een jaarlijkse blijk van waardering in aanmerking worden gebracht.</t>
         </is>
       </c>
     </row>
@@ -2336,19 +2422,22 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>GM0873</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Artikel 17 &gt; lid 1</t>
+          <t>Hattem</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1. Mantelzorgers van cliënten in de gemeente kunnen door middel van een melding bij het Steunpunt mantelzorg voor het ontvangen van een jaarlijkse blijk van waardering in aanmerking worden gebracht.</t>
+          <t>Hoofdstuk 3 Afwegingskader &gt; 3.8 Algemene voorzieningen</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1. Er zijn veel verschillende algemene voorzieningen. Een algemene voorziening wordt bekostigd of gefaciliteerd door de gemeente. Voorbeelden binnen de gemeente Hattem:
+• SPOOR inclusief het Geheugensteunpunt, mantelzorg- en vrijwilligersondersteuning bij Stichting Welzijn Hattem;
+• Hulp bij thuisad</t>
         </is>
       </c>
     </row>
@@ -2358,20 +2447,21 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>GM0753</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOOFDSTUK 1 ALGEMENE BEPALINGEN &gt; Artikel 1.1 Begripsomschrijvingen &gt; lid 1</t>
+          <t>Beekdaelen</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>In deze nadere regels wordt verstaan onder:
-a. Mantelzorg: hulp ten behoeve van zelfredzaamheid, participatie, jeugdhulp, het opvoeden en opgroeien van jeugdigen en zorg en overige diensten als bedoeld in de Zorgverzekeringswet, die niet binnen de gebruikelijke zorg valt, rechtstreeks voortvloeit ui</t>
+          <t>5. Mantelzorgbeleid &gt; 5.2 Ondersteunen &gt; deel 2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Het Steunpunt verzorgt ondersteuning aan de mantelzorgers die hier behoefte aan hebben. Het steunpunt biedt op diverse manieren ondersteuning, naar behoefte en op maat, aan de mantelzorgers. Vanuit Ruggesteun kunnen hierbij vrijwilligers worden ingezet.
+Deze ondersteuning bestaat uit een aantal basi</t>
         </is>
       </c>
     </row>
@@ -2381,21 +2471,21 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>GM1954</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5. Mantelzorgbeleid &gt; 5.3 Waarderen &gt; deel 3</t>
+          <t>Elburg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Voor alle aanvragen en bovengenoemde ‘automatische’ verstrekkingen blijven dezelfde vijf voorwaarden gelden:
-1. De mantelzorger verleent langer dan 3 maanden en meer dan 8 uur per week onbetaalde zorg aan een naaste (degene die mantelzorg ontvangt)
-2. De mantelzorger staat geregistreerd (vóór einde </t>
+          <t>1.8.1 Eigen oplossingen &gt; Uitzonderingen</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>In bepaalde gevallen kan een inwoner, ondanks de aanwezigheid van een of meerdere huisgenoten, toch in aanmerking komen voor een maatwerkvoorziening. Bijvoorbeeld in de volgende gevallen:
+- Wanneer de partner of huisgenoot gezondheidsproblemen en beperkingen heeft en of door de combinatie met het vo</t>
         </is>
       </c>
     </row>
@@ -2405,20 +2495,20 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>GM0668</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hoofdstuk 9. MANTELZORGONDERSTEUNING &gt; Artikel 9.4 Voorwaarden en verplichtingen</t>
+          <t>Oldebroek</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>a. Mantelzorgmakelaar
-- De door de gemeente aanbestede of gesubsidieerde partij tot mantelzorgondersteuning (Steunpunt Mantelzorg) stelt voorafgaand vast dat de diensten van een mantelzorgmakelaar niet op een andere manier worden vergoed. Bijvoorbeeld door de werkgever of vanuit de aanvullende zorgv</t>
+          <t>Hoofdstuk 2 Maatwerkvoorzieningen &gt; 2.7 Logeeropvang functie respijtzorg</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Logeeropvang of ook wel kortdurend verblijf genoemd, is een vorm van maatwerkondersteuning. Inzet is mogelijk vanuit verschillende wetten. Vanuit de Wmo valt inzet onder het bevorderen of stabiliseren van de zelfredzaamheid van de inwoner. In de meeste gevallen is de inzet van logeeropvang een vorm </t>
         </is>
       </c>
     </row>
@@ -2433,7 +2523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2444,35 +2534,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_gemeenten</t>
+          <t>n_gemeenten_corpus</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>n_passages</t>
+          <t>n_passages_corpus</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sectietype_verdeling</t>
+          <t>n_gemeenten_filter</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>domein_verdeling</t>
+          <t>n_passages_filter</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>categorie_verdeling (heel corpus)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>voorbeeld_gemeente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>voorbeeld_pad</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>voorbeeld_tekst</t>
         </is>
@@ -2490,27 +2585,28 @@
       <c r="C2" t="n">
         <v>14</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>artikel=10; toelichting_artikel=3; bijlage=1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>jeugd=9; wmo=4; beide=1</t>
-        </is>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GM0262</t>
+          <t>jeugd=9; kern=5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Lochem</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Hoofdstuk 5 Wonen in een veilige en gezonde omgeving &gt; Artikel 5.2.2 Wat kunnen we doen bij (dreigende) overbelasting van de mantelzorger?</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Mantelzorgers leveren een grote bijdrage aan de doelen van de Wmo. Daarom is het belangrijk dat mantelzorgers zo lang mogelijk hun zorg kunnen leveren. In het geval van (dreigende) overbelasting van de mantelzorger, kunnen we een maatwerkvoorziening inzetten om de mantelzorger te ontlasten. Met de v</t>
         </is>
@@ -2522,19 +2618,20 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>GM0553</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Toelichting &gt; Artikel 4 &gt; Artikel 4 Toegang individuele voorziening &gt; 1. het aanspreken van een aanvullende verzekering;</t>
+          <t>Borne</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>De feitelijke situatie is het uitgangspunt bij het vaststellen of en in welke mate gebruikelijke hulp geboden kan worden of dat juist sprake is van (dreigende) overbelasting. De vraag is dus of in individuele situaties sprake is van een uitzondering op grond waarvan toch gebruikelijke zorgtaken moet</t>
+          <t>Hoofdstuk 5. Afweging en voorwaarden maatwerkvoorzieningen &gt; Artikel 5.1 Criteria maatwerkvoorzieningen &gt; lid 3 &gt; deel 6</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Mantelzorg betreft ondersteuning voor een naaste ten behoeve van diens zelfredzaamheid en participatie, die qua omvang en intensiteit de gebruikelijke hulp overstijgt en die rechtstreeks voortkomt uit de sociale relatie tussen personen. Mantelzorg wordt niet verleend in het kader van een hulpverlene</t>
         </is>
       </c>
     </row>
@@ -2544,20 +2641,20 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>GM0613</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1. Afwegingskader Jeugdhulp &gt; 1.2 Eigen verantwoordelijkheid en probleemoplossend vermogen &gt; Artikel 1.2.1 Onvoldoende eigen mogelijkheden en probleemoplossend vermogen</t>
+          <t>Zutphen</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Het kan zijn dat het ouders op het moment van onderzoek niet lukt om alle hulp zelf te bieden. Het kan zijn door overbelasting (niet samenhangend met de zorg aan het kind), door werk, door gebrek aan vaardigheden, door eigen problematiek, etc.
-Wat hebben ouders nodig om het wel te kunnen, of om meer</t>
+          <t>Hoofdstuk 4 Maatwerkvoorzieningen &gt; Artikel 4.1.5 Overbelasting</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Bij zowel mantelzorg als wanneer de ondersteuning wordt betaald vanuit pgb is het van belang te onderzoeken of er sprake is van (dreigende) overbelasting. De EDIZ-vragenlijst helpt inzichtelijk te maken of hiervan sprake is. Voorbeelden van symptomen die kunnen wijzen op dreigende overbelasting: ang</t>
         </is>
       </c>
     </row>
@@ -2567,19 +2664,20 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>GM0301</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hoofdstuk 4 Maatwerkvoorzieningen &gt; Artikel 4.1.5 Overbelasting</t>
+          <t>Putten</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bij zowel mantelzorg als wanneer de ondersteuning wordt betaald vanuit pgb is het van belang te onderzoeken of er sprake is van (dreigende) overbelasting. De EDIZ-vragenlijst helpt inzichtelijk te maken of hiervan sprake is. Voorbeelden van symptomen die kunnen wijzen op dreigende overbelasting: ang</t>
+          <t>2. De hulpvraag &gt; Artikel 2.4. (Dreigende) overbelasting</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Mantelzorgers leveren een grote bijdrage aan de doelen van de Wmo. Daarom is het belangrijk dat mantelzorgers zo lang mogelijk in staat zijn hun zorg te leveren. In het geval van (dreigende) overbelasting kan een maatwerkvoorziening of pgb worden ingezet om de mantelzorger langdurig in staat te stel</t>
         </is>
       </c>
     </row>
@@ -2589,20 +2687,21 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>GM0484</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.2.1 Onvoldoende eigen mogelijkheden en probleemoplossend vermogen</t>
+          <t>Bodegraven-Reeuwijk</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Het kan zijn dat het ouders op het moment van onderzoek niet lukt om alle hulp zelf te bieden. Het kan zijn door overbelasting (niet samenhangend met de zorg aan het kind), door werk, door gebrek aan vaardigheden, door eigen problematiek, etc.
-Wat hebben ouders nodig om het wel te kunnen, of om meer</t>
+          <t>Artikel 12. &gt; deel 4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Beoordeling van overbelasting
+De feitelijke situatie is het uitgangspunt bij het vaststellen of en in welke mate er gebruikelijke hulp geboden kan worden of dat er juist sprake is van (dreigende) overbelasting. De vraag is dus of in individuele situaties er sprake is van een uitzondering op grond wa</t>
         </is>
       </c>
     </row>
@@ -2618,35 +2717,31 @@
       <c r="C7" t="n">
         <v>470</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>artikel=337; bijlage=107; toelichting_algemeen=8; toelichting_artikel=6; begrippen=5; bijlage_pdf=5; aanhef=2</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>wmo=379; jeugd=54; beide=32; onbekend=5</t>
-        </is>
+      <c r="D7" t="n">
+        <v>74</v>
+      </c>
+      <c r="E7" t="n">
+        <v>239</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GM0200</t>
+          <t>kern=330; buiten_scope=55; jeugd=55; twijfel=16; aanbod=14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bijlage</t>
+          <t>Noordenveld</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bijlage
-3:
-Zelfredzaamheidsmatrix (ZRM)
-Deze matrix kan worden toegepast bij de beoordeling van een hulpvraag op grond van het 5 stappenplan van de CRvB. Met deze matrix wordt de situatie van de inwoner op verschillende levensdomeinen in kaart gebracht.
-Toelichting:
-Score 5: volledig zelfredzaam,
-Sc</t>
+          <t>HOOFDSTUK 3 RESULTATEN &gt; Artikel 2 Domeinen en resultaatgebieden &gt; deel 63</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• er kan sprake zijn van complexe en meervoudige problemen die maken dat intensievere ondersteuning nodig is dan thuis of in een pleeggezin geboden kan worden;
+• dit resultaatgebied omvat mede de dagelijkse verzorging van de jeugdige, zoals het bieden van een slaapplaats en voeding en de dagelijkse </t>
         </is>
       </c>
     </row>
@@ -2656,19 +2751,23 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>GM0642</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hoofdstuk 5 Beschermd wonen &gt; Artikel 5.8 Dagbesteding &gt; lid 4</t>
+          <t>Bladel</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4. Bij de indicatiestelling worden de beoogde resultaten geformuleerd, waarbij wordt aangesloten bij de resultaatgebieden van de ZRM. Het ondersteuningsplan (opgesteld door aanbieder in overeenstemming met de cliënt) moet hierop worden gebaseerd en maakt onderdeel uit van de beschikking. In het onde</t>
+          <t>Hoofdstuk 3: Aanvraag maatwerkvoorziening &gt; Artikel 9. Voorwaarden maatwerkvoorziening &gt; deel 15</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Begeleiding
+Begeleiding is in de wet gedefinieerd als activiteiten gericht op het bevorderen van zelfredzaamheid en participatie van de cliënt, zodat hij zo lang mogelijk in zijn eigen leefomgeving kan blijven wonen.
+Indiceren Begeleiding
+Om de hulpvraag te objectiveren en hierdoor richting te geven</t>
         </is>
       </c>
     </row>
@@ -2678,19 +2777,20 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>GM1954</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 6</t>
+          <t>Leeuwarden</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Maatschappelijke participatie | • niet van toepassing door crisissituatie of in ‘overlevingsmodus’ of veroorzaakt ernstige overlast | • maatschappelijk geïsoleerd of veroorzaakt overlast | • nauwelijks participerend in maatschappij (bijwonen) of uitsluitend zorgtaken | • enige maatschappelijke parti</t>
+          <t>Artikel 22. Beschermd wonen &gt; lid 4 &gt; deel 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Er is sprake van psychische en/of psychosociale problematiek. Er is behoefte aan onplanbare ondersteuning in de vorm van groepswonen voor personen van 16 jaar met daarbij behorend 24/7 bereikbaarheid en beschikbaarheid. De persoon is in staat om hulp te vragen en beschikt over basisvaardigheden om z</t>
         </is>
       </c>
     </row>
@@ -2700,19 +2800,21 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>GM0845</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Toelichting &gt; Algemeen &gt; Kleinschalig beschermd wonen</t>
+          <t>Beuningen</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1. De inwoner ervaart meerwaarde van het kleinschalig wonen door het contact met medebewoners en de gedeeltelijke groepsgewijze begeleiding. De kleinschalige woonvorm kan in diverse vormen tot uiting komen. De inwoner huurt of bezit zelf een woning/kamer. Kenmerkend voor dit product is dat er sprake</t>
+          <t>1.5 Het gesprek</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bij het gesprek ligt het accent op zorgvuldigheid en transparantie en het heeft als doel:
+-Het helder maken welke keuzes zijn gemaakt aan de hand van de onderwerpen die in het gesprek en onderzoeksverslag aan bod moeten komen: uit het onderzoeksverslag moet duidelijk worden in hoeverre de behoeften </t>
         </is>
       </c>
     </row>
@@ -2722,24 +2824,22 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>GM0512</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Toelichting &gt; Artikel 4.8 &gt; Bepalen urgentie</t>
+          <t>Noordenveld</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Voor het bepalen van een urgente situatie hanteren we de Zelfredzaamheidsmatrix (ZRM). Daarbij zijn de volgende indicatoren van belang.
-a. Geestelijke en lichamelijke Gezondheid
-b. Activiteiten van het Dagelijks Leven (ADL)
-c. Sociaal netwerk
-d. Financiën
-Een cliënt wordt als “urgent” gekwalificeerd</t>
+          <t>HOOFDSTUK 3 RESULTATEN &gt; Artikel 2 Domeinen en resultaatgebieden &gt; deel 34</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• dit hoofdresultaat wordt ingezet voor de duur van 2 jaar.
+Resultaat bij volledige zelfredzaamheid (ZRM)
+De symptomen van de problematiek zijn afwezig of zeldzaam of de symptomen van de problematiek hebben beperkte invloed op het dagelijks functioneren en het functioneren bij diverse activiteiten. </t>
         </is>
       </c>
     </row>
@@ -2753,31 +2853,33 @@
         <v>149</v>
       </c>
       <c r="C12" t="n">
-        <v>294</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>artikel=185; bijlage=86; ondertekening=6; bijlage_pdf=6; toelichting_artikel=5; toelichting_algemeen=3; aanhef=2; begrippen=1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>wmo=185; jeugd=90; beide=13; onbekend=6</t>
-        </is>
+        <v>293</v>
+      </c>
+      <c r="D12" t="n">
+        <v>40</v>
+      </c>
+      <c r="E12" t="n">
+        <v>51</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GM1731</t>
+          <t>kern=91; twijfel=90; jeugd=86; aanbod=19; buiten_scope=6; waardering=1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Participatie</t>
+          <t>Doetinchem</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>De deelnemers aan de pilot worden verplicht tot participatie. Het is aan de initiatiefnemer om de manier van participatie te bepalen, omdat dit maatwerk betreft. Dit kunnen bijvoorbeeld keukentafelgesprekken, enquêtes of vragenlijsten zijn. Hiervan dient een verslag te worden gemaakt, dat tevens een</t>
+          <t>2. De hulpvraag &gt; Artikel 2.4 Het onderzoek/stappenplan &gt; deel 4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantelzorg
+Mantelzorg betreft ondersteuning voor een naaste ten behoeve van diens zelfredzaamheid en participatie, die qua omvang en intensiteit de gebruikelijke hulp overstijgt en die rechtstreeks voortkomt uit de sociale relatie tussen personen. Mantelzorg wordt niet verleend in het kader van een </t>
         </is>
       </c>
     </row>
@@ -2787,26 +2889,21 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>GM0531</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bijlage &gt; 1. Vroegtijdig inzet van de benodigde deskundigheid in het hulpverleningsproces;</t>
+          <t>Maastricht</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Functieprofiel | HBO/WO
-Functiemix | Wordt hoofdzakelijk door WO geschoold personeel uitgevoerd. In mindere mate kan naast de WO-er ondersteunend HBO of WO+ geschoold personeel ingezet worden.
-Regiebehandelaar | Ja
-Groepsgrootte | n.v.t.
-Specialistische diagnostiek
-Normenkader
-Eenheid | Minuten
-Duur</t>
+          <t>Hoofdstuk 4. Slotbepalingen &gt; Artikel 19: CITEERTITEL EN INWERKINGTREDING &gt; lid 3 &gt; 4. Richtlijn bij (dreigende) overbelasting van partner, ouder, volwassen kind en/of andere huisgenoten</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ALGEMEEN
+De zorg voor een ziek kind of een zieke partner, kan zo zwaar worden dat van overbelasting sprake is. In de meeste gevallen is de bovengebruikelijke hulp die geïndiceerd wordt voldoende om deze overbelasting te voorkomen. Maar soms blijkt deze geïndiceerde hulp niet voldoende te zijn. In zu</t>
         </is>
       </c>
     </row>
@@ -2816,24 +2913,22 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>GM0183</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 1</t>
+          <t>Schagen</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bijlage
-Stand van zaken duurzaamheid in de gemeente Dinkelland en Tubbergen
-Behoort bij uitvoeringsprogramma “Op weg naar de duurzame gemeenten Dinkelland en Tubbergen 2016-2021”
-1.
-Inleiding
-In het Coalitieprogramma Dinkelland 2014-2018 en het Coalitieakkoord Tubbergen 2014-2018 heeft Duurzaamheid </t>
+          <t>Hoofdstuk 7 Inkomen en schulden &gt; 7.4 Schuldhulpverlening &gt; Artikel 7.4.1 Begrippen &gt; lid 1 &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1. In de beleidsregels onder 7.4 wordt verstaan onder:
+a. betalingsregeling: bij overeenkomst tussen schuldenaar en schuldeiser(s) vastgestelde regeling, waarin wordt bepaald dat de vastgestelde vordering(en) volledig wordt/worden terugbetaald in een vooraf vastgesteld aantal termijnen;
+b. budgetbeh</t>
         </is>
       </c>
     </row>
@@ -2843,19 +2938,20 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>GM0935</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Verzuimprotocol &gt; NB: &gt; deel 24</t>
+          <t>Middelburg (Z.)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Het gaat concreet om medewerkers die na een toekenning van een WGA-uitkering binnen de organisatie zijn herplaatst en medewerkers die wegens arbeidsongeschiktheid zijn ontslagen. Gedurende de eerste 10 jaar na toekenning van de uitkering is de gemeente verantwoordelijk voor de re-integratie van de (</t>
+          <t>Hoofdstuk 7. Evaluatie &gt; 7.1 Cliëntervaringsonderzoeken</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>De gemeente is wettelijk verplicht zowel voor Wmo als Jeugd jaarlijks te onderzoeken hoe cliënten de kwaliteit van de maatschappelijke ondersteuning of geleverde jeugdhulp ervaren en de resultaten jaarlijks voor 1 juli te publiceren. Voor de Wmo is er landelijk een verplichte standaardvragenlijst di</t>
         </is>
       </c>
     </row>
@@ -2865,21 +2961,20 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>GM0189</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 2</t>
+          <t>Hulst</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>• bijkomende relationele problemen.
-Onderzoek naar de draaglast-draagkracht mantelzorger
-Het kan soms heel duidelijk zijn dat de mantelzorger overbelast is, in ander gevallen is dat minder duidelijk en zal dit in het indicatieonderzoek moeten worden uitgediept. Er bestaat niet één, simpel af te neme</t>
+          <t>Hoofdstuk 6: Monitoring en evaluatie &gt; Cliëntervaringsonderzoek</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Om erachter te komen of beleid de juiste impact maakt, bevragen we inwoners via het cliëntervaringsonderzoek. Dit doen we voor inwoners die gebruik maken van een voorziening vanuit de Wmo en vanuit de Jeugdwet. In samenwerking met bureau Lorenz stelden we een online vragenlijst op die inwoners makke</t>
         </is>
       </c>
     </row>
@@ -2895,51 +2990,28 @@
       <c r="C17" t="n">
         <v>3</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>artikel=3</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>wmo=3</t>
-        </is>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GM0826</t>
+          <t>kern=2; twijfel=1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Indicatieprotocol voorzieningen maatschappelijke ondersteuning &gt; Indicatieprocedure &gt; deel 1</t>
+          <t>Oosterhout</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Eerste gesprek
-De eerste melding zal over het algemeen telefonisch gebeuren of door melding bij het loket. Daarbij wordt de keuze gemaakt of het een eenvoudige (vervolg) aanvraag betreft of dat uitgebreider onderzoek noodzakelijk is (bij complexere problematiek) of door de cliënt gewenst is.
-Voor he</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>GM0826</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
           <t>Indicatieprotocol voorzieningen maatschappelijke ondersteuning &gt; Indicatie-instrumenten</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Gespreksleidraad
 Indicatieschema
@@ -2951,65 +3023,90 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Oosterhout</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Indicatieprotocol voorzieningen maatschappelijke ondersteuning &gt; Indicatieprocedure &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Eerste gesprek
+De eerste melding zal over het algemeen telefonisch gebeuren of door melding bij het loket. Daarbij wordt de keuze gemaakt of het een eenvoudige (vervolg) aanvraag betreft of dat uitgebreider onderzoek noodzakelijk is (bij complexere problematiek) of door de cliënt gewenst is.
+Voor he</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>checklist</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" t="n">
+        <v>229</v>
+      </c>
+      <c r="D19" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" t="n">
+        <v>51</v>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GM0627</t>
+          <t>twijfel=104; kern=70; jeugd=28; aanbod=21; buiten_scope=6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4 Uitvoering en samenwerking &gt; 4.2 Op welke wijze worden deze specifieke doelgroepen betrokken bij de planvorming?</t>
+          <t>Ooststellingwerf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>De inwoners worden in Waddinxveen betrokken bij het formuleren van nieuwe beleid. Voor het formuleren van het Leefstijlplan zijn de inwoners niet apart benaderd. Het Leefstijlplan staat niet op zichzelf, maar wordt verbonden aan ons huidige beleid of nog nieuw te formuleren beleid.
-Alle organisaties</t>
+          <t>Hoofdstuk 2 – Persoonsgebonden budget &gt; Hoofdregel</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">: Degene die het pgb gaat beheren mag niet dezelfde persoon zijn als degene die de ondersteuning gaat uitvoeren. Daarnaast zal over het algemeen de persoon uit het sociaal netwerk, de beheerstaken kosteloos uitvoeren. Het pgb-budget mag (bijvoorbeeld) niet worden aangewend om iemand uit het sociaal </t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>checklist</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>100</v>
-      </c>
-      <c r="C20" t="n">
-        <v>226</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>artikel=134; bijlage=68; aanhef=16; toelichting_artikel=4; toelichting_algemeen=4</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>wmo=182; jeugd=34; beide=10</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>GM0935</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bijlage &gt; 3. Balletbegeleider</t>
+          <t>Breda</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2. Emotionele piekbelasting | Signaalvragen (mondeling of schriftelijk) naar:; - recent doorgemaakt trauma; Inzet gevalideerd screeningsinstrument ter detectie van de huidige aanwezigheid van:; - posttraumatische stressklachten (checklist)
-Bijzondere functie-eis: | Aspect van de belastbaarheid wat o</t>
+          <t>Hoofdstuk 7 Persoonsgebonden budget &gt; Artikel 7.4.2 Algemene beoordeling pgb-bekwaamheid &gt; lid 10</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10. Weten wat de budgethouder moet doen als werkgever of opdrachtgever van een ondersteuner. Het is niet erg als de cliënt sommige regels over hoe een werkgever of opdrachtgever moet zijn niet kent. Bijvoorbeeld bij ontslag van een ondersteuner. Maar de client moet de informatie daarover wel zelf ku</t>
         </is>
       </c>
     </row>
@@ -3019,20 +3116,21 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>GM0301</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hoofdstuk 7 Beleidsvoorschriften Uitvoeringszaken &gt; 7.1 De aanvraagprocedure</t>
+          <t>Vijfheerenlanden</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Een bijstandsuitkering wordt niet automatisch toegekend. Er is een aanvraag voor nodig.
-Een uitkering kan digitaal worden aangevraagd via UWV (www.werk.nl). Voor deze digitale aanvraag is een digitale hand tekening nodig. Dat is een DigiD, een code, die bestaat uit cijfers, letters en andere tekens.</t>
+          <t>Hoofdstuk 3 Voorzieningen &gt; Artikel 3.1 Voorzieningen Jeugdhulp en Wmo &gt; lid 6 &gt; deel 9</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>De verantwoordelijkheid ligt bij de inwoner om uit te zoeken of er een stalling gerealiseerd mag worden, bijvoorbeeld bij de Vereniging van Eigenaren of de woningcorporatie.
+Extra aanpassingen welke noodzakelijk zijn als gevolg van de indeling van tuin of terras, afmetingen van door de inwoner aange</t>
         </is>
       </c>
     </row>
@@ -3042,24 +3140,23 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>GM0779</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 1</t>
+          <t>Nieuwkoop</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bijlage
-I Checklist participatietraject
-A. Check vooraf
-Niet ieder project leent zich voor een participatietraject. Het project moet voldoen aan de volgende criteria:
-• Het participatietraject draagt bij aan het ontwikkelen, uitvoeren of evalueren van beleid
-• Het doel van het participatietraject is</t>
+          <t>Hoofdstuk 2 Aanvraag- en beoordelingsprocedure &gt; Artikel &gt; lid 9 &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voorwaarden voor de besteding van het pgb
+Het college verstrekt een pgb aan inwoners onder de voorwaarde dat:
+a. De inwoner samen met een medewerker van het integraal ondersteuningsteam een verslag of integraal plan opgesteld heeft en een budgetplan, waarin benoemd is:
+- dat een maatwerkvoorziening </t>
         </is>
       </c>
     </row>
@@ -3069,48 +3166,21 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>GM0569</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &gt; deel 43</t>
+          <t>Bronckhorst</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Criteria pré-mantelzorgwoningen
-Een checklist met criteria biedt een leidraad bij het beoordelen van een vergunningaanvraag voor een pré-mantelzorgwoning. Met het vaststellen van onderstaande criteria door het college heeft de gemeente een richtlijn voor de beoordeling van vergunningaanvragen.
-Defin</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>GM0779</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Inhoudsopgave &gt; 5.3 Handreiking voor de organisatie 13</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Bijlage I Checklist participatietraject 16
-Bijlage II Format 8 stappenplan participatie 19
-Bijlage III: Participatietrap en ringen van invloed 21
-Bijlage IV: Format opzet participatieplan 22
-Bijlage V: Overzicht participatie-instrumenten 23
-Gebruikte literatuur 24</t>
+          <t>Uitvoeringsprogramma 5: Iedereen een stevige basis &gt; 5.2. Wegnemen en voorkomen belemmeringen &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ACTIVITEIT; Invoeren voorzieningencheck, minimaregeling in natura, eenmalige tegemoetkoming energiebesparing
+TOELICHTING; 1. Landelijk is in het nieuws geweest dat veel mensen geen gebruik maken van voorzieningen als huur- of zorgtoeslag. Dit blijkt in onze gemeente ook zo te zijn (CBS 2019). Dit le</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3136,35 +3206,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_gemeenten</t>
+          <t>n_gemeenten_corpus</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>n_passages</t>
+          <t>n_passages_corpus</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sectietype_verdeling</t>
+          <t>n_gemeenten_filter</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>domein_verdeling</t>
+          <t>n_passages_filter</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>categorie_verdeling (heel corpus)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>voorbeeld_gemeente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>voorbeeld_pad</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>voorbeeld_tekst</t>
         </is>
@@ -3180,34 +3255,32 @@
         <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>282</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>artikel=220; bijlage=34; begrippen=8; toelichting_artikel=6; toelichting_algemeen=5; bijlage_pdf=5; aanhef=4</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>wmo=251; jeugd=13; beide=13; onbekend=5</t>
-        </is>
+        <v>281</v>
+      </c>
+      <c r="D2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E2" t="n">
+        <v>186</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GM0718</t>
+          <t>kern=158; waardering=57; aanbod=37; twijfel=16; jeugd=13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Inleiding &gt; Artikel  Subsidieregel 5 - Ondersteuning mantelzorgers en vrijwilligers &gt; deel 1</t>
+          <t>Heerde</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1. Doelstelling activiteiten.
-1.a. Mantelzorgactiviteiten te ondersteunen die gericht zijn op het waarderen, stimuleren en ondersteunen van mantelzorgers en vrijwilligers, zoals beschreven in de nota Onbetaalbare Kracht.
-2. Diensten / (ondersteuning)Activiteiten / Producten.
-Mantelzorgers moeten kun</t>
+          <t>3. Benut de kracht van de samenleving &gt; Artikel</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>In de gemeente Heerde is 18% van de inwoners mantelzorger. Van de mantelzorgers geeft 2% aan zwaar belast te zijn. Het aantal mantelzorgers in Heerde is licht toegenomen en ligt hoger dan het landelijk gemiddelde met 14% mantelzorgers. Het aantal ontvangers van mantelzorg is toegenomen, van 11% in 2</t>
         </is>
       </c>
     </row>
@@ -3217,19 +3290,20 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>GM0432</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hoofdstuk 3. Subsidieprogramma 2020-2023 zonder uitvoeringsovereenkomsten &gt; Paragraaf 3.2 Gemeentelijke beleidsdoelen en doelgroepen &gt; Artikel 3.2.2 Doelgroepen</t>
+          <t>Kampen</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>De activiteit waarvoor subsidie wordt aangevraagd moet in ieder geval gericht zijn op de inwoners/ organisaties in gemeente Opmeer. De aanvraag wordt versterkt indien de aanvrager de doelgroep(en) specificeert en aansluit bij één of meerdere doelgroepen uit het gemeentelijk beleid, zoals hieronder v</t>
+          <t>5. Wonen in een veilige en gezonde omgeving &gt; Artikel 5.3.3 Voorwaarden en aanvraagprocedure mantelzorgwaardering &gt; lid 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2. Alleen de mantelzorger kan de mantelzorgwaardering aanvragen. In geval van een jonge mantelzorger kan een van de ouders/verzorgers de waardering, namens de jongere, aanvragen.</t>
         </is>
       </c>
     </row>
@@ -3239,20 +3313,20 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>GM0171</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hoofdstuk 4 Gebruikelijke hulp &gt; Artikel 4.5 In redelijkheid te verwachten van huisgenoten &gt; 4.5.4 Overname van huishoudelijke taken</t>
+          <t>Beekdaelen</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>• Kinderen vanaf 13 jaar kunnen, naast bovengenoemde taken, hun eigen kamer op orde houden, d.w.z. rommel opruimen, stofzuigen, bed verschonen. Ook kunnen zij geïnstrueerd worden was te sorteren, de wasmachine of wasdroger aan te zetten en de was op te vouwen en op te ruimen.
-• Kinderen vanaf 18 jaa</t>
+          <t>3. Wat is mantelzorg? &gt; 3.1 Wie zijn onze mantelzorgers?</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Mantelzorgers zijn bescheiden en zetten zichzelf niet snel in de schijnwerpers. Ze vinden het gewoon om hun naaste te helpen. Uit gesprekken met mantelzorgers blijkt dat ook niet iedere mantelzorger zichzelf herkent als mantelzorger. Met name bij jonge mantelzorgers is dat het geval. Mantelzorgers z</t>
         </is>
       </c>
     </row>
@@ -3262,19 +3336,22 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>GM1700</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4 Bijlagen &gt; 4.2 BIJLAGE Uitwerking (visie) Informele zorg &gt; deel 2</t>
+          <t>Bunnik</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Werkende mantelzorgers zijn mensen die mantelzorg naast hun baan uitvoeren. In Twenterand zien we dat er voornamelijk winst te behalen is in de bewustwording bij werkgevers en op de werkvloer over de stress en de gevolgen die deze combinatie met zich meebrengt. Daarnaast is het van belang dat werkge</t>
+          <t>Artikel 4 Vorm en hoogte mantelzorgwaardering &gt; lid 2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2. De mantelzorgwaardering voor jonge mantelzorgers bestaat uit:
+a. een waardebon ter waarde van maximaal €50,-, en/of
+b. een of meerdere georganiseerde activiteiten;</t>
         </is>
       </c>
     </row>
@@ -3284,21 +3361,23 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>GM1940</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 4</t>
+          <t>Lelystad</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>• Ruimte voelen om je open te kunnen stellen.
-Jonge mantelzorger
-Deelname</t>
+          <t>4.3 Huidige lokale inzet &gt; 2. Activerende huisbezoeken (LPPO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4. Steunpunt Mantelzorg
+In de gemeente Lelystad is een Steunpunt Mantelzorg (ondergebracht bij Axion) actief. Daar werken diverse mantelzorgconsulenten die ondersteuning en begeleiding bieden aan mantelzorgers. Het Steunpunt Mantelzorg biedt mantelzorgers:
+• Emotionele ondersteuning;
+• Ondersteuning</t>
         </is>
       </c>
     </row>
@@ -3312,32 +3391,36 @@
         <v>335</v>
       </c>
       <c r="C7" t="n">
-        <v>2789</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>artikel=1517; bijlage=819; begrippen=163; toelichting_artikel=149; aanhef=65; ondertekening=33; toelichting_algemeen=32; bijlage_pdf=11</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>wmo=1772; jeugd=678; beide=328; onbekend=11</t>
-        </is>
+        <v>2786</v>
+      </c>
+      <c r="D7" t="n">
+        <v>312</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1264</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GM0678</t>
+          <t>kern=2148; jeugd=588; twijfel=25; buiten_scope=21; waardering=2; aanbod=2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Artikel</t>
+          <t>Rijswijk (ZH.)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>De maatwerkvoorziening voor huishoudelijke ondersteuning kan worden ingezet voor het bereiken van resultaten onder de domeinen ‘Huisvesting en huishouden’ en ‘Zorg voor kinderen’. Huishoudelijke ondersteuning is niet aan de orde als gebruikelijke hulp aanwezig is.
-Daarnaast wordt geen voorziening hu</t>
+          <t>HOOFDSTUK 1. DEFININTIE &gt; Artikel 1. Definitiebepalingen &gt; lid 2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aanvullend wordt in deze verordening en de daarop berustende bepalingen verstaan onder:
+a. algemeen gebruikelijke voorziening is een voorziening die:
+1. niet specifiek bedoeld is voor personen met een beperking;
+2. daadwerkelijk beschikbaar is;
+3. een passende bijdrage levert aan het realiseren van </t>
         </is>
       </c>
     </row>
@@ -3347,19 +3430,24 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>GM0180</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4. Overwegingen bij een maatwerkvoorziening &gt; Gebruikelijke hulp &gt; deel 1</t>
+          <t>Berkelland</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Gebruikelijke hulp is hulp of ondersteuning waarvan het gebruikelijk is dat huisgenoten en/of directe familieleden dit voor elkaar doen. Dit betekent bijvoorbeeld bij het huishouden dat, als inwoner zelf het huishouden niet meer kan doen, de huisgenoten die taken in principe moeten overnemen. Maar o</t>
+          <t>Hoofdstuk 1 De toegang naar maatschappelijke ondersteuning en jeugdhulp &gt; 1.4 Vaststellen mogelijkheden inwoner &gt; Artikel 1.4.2 Gebruikelijke hulp &gt; deel 3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>b. Frequentie en patroon van de zorghandelingen
+Zorghandelingen die meelopen in het normale patroon van dagelijkse zorg voor een
+kind
+, zoals 3 keer eten per dag, kunnen als gebruikelijke hulp worden aangemerkt.
+Bij de beoordeling wordt rekening gehouden met die zorgsituaties waarbij ouders voortdur</t>
         </is>
       </c>
     </row>
@@ -3369,22 +3457,21 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>GM0388</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bijlage &gt; deel 1</t>
+          <t>Diemen</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bijlage
-Richtlijnen ten aanzien van gebruikelijke hulp van ouders voor kinderen met een normaal ontwikkelingsprofiel in verschillende levensfasen van het kind in relatie tot individuele maatwerkvoorzieningen op grond van Wmo en Jeugdwet
-Kinderen van 0 tot 3 jaar
-• hebben 24 uur per dag zorg in de na</t>
+          <t>7. Maatwerkvoorziening: hulp bij het huishouden &gt; Artikel 7.3. Gebruikelijke hulp &gt; deel 2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Er wordt geen onderscheid gemaakt op basis van sekse, religie, cultuur, de wijze van inkomensverwerving of persoonlijke opvattingen over het verrichten van huishoudelijke taken.
+Bij de bepaling van gebruikelijke hulp wordt rekening gehouden met de eventuele beperking(en) van de huisgenoot of huisgen</t>
         </is>
       </c>
     </row>
@@ -3394,20 +3481,20 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>GM0405</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hoofdstuk 2 Toegang &gt; Artikel 2.5 Beoordeling aanwezigheid gebruikelijke hulp &gt; lid 4</t>
+          <t>Heiloo</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4. Wanneer er gebruikelijke hulp van een minderjarig kind wordt verwacht, wordt onderzoek gedaan naar het vermogen van dit kind. De inzet van kinderen mag niet ten koste gaan van hun welbevinden en ontwikkeling, waaronder schoolprestaties. Er wordt rekening gehouden met:
-a. wat op een bepaalde leeft</t>
+          <t>Hoofdstuk 1 Algemene bepalingen &gt; Artikel 1. Begrippen &gt; lid 2 &gt; deel 3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>k. Gebruikelijke hulp: ondersteuning of zorg die naar algemeen aanvaarde opvattingen in redelijkheid mag worden verwacht van de echtgenoot/levenspartners, ouders en/of andere verzorgers of opvoeders, inwonende kinderen of andere huisgenoten, ook al is er sprake van een Belanghebbende met een ziekte,</t>
         </is>
       </c>
     </row>
@@ -3417,19 +3504,20 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>GM0168</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6 Huishoudelijke ondersteuning &gt; 6.12 Normenkader huishoudelijke ondersteuning HHM 2019 &gt; Artikel 6.12.6 Kamer wel/niet in gebruik (als slaapkamer)</t>
+          <t>Oostzaan</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Binnen het normenkader rekenen we extra tijd voor extra kamers. Er is een verschil tussen de tijd die wordt gerekend wanneer een extra kamer ‘wel of niet in gebruik’ is. Een extra kamer ‘in gebruik als slaapkamer’ of een extra kamer ‘niet in gebruik als slaapkamer’. Als het geen slaapkamer is, dan i</t>
+          <t>Hoofdstuk 2. Ondersteuning en regie bij het voeren van een huishouden &gt; Artikel 6. Thuis zorgen voor kinderen onder de 6 jaar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Het zorgen voor kinderen is een taak van ouder en/of verzorgers. Dat geldt ook voor ouders die door beperkingen niet in staat zijn hun kinderen te verzorgen. Elke ouder is zelf verantwoordelijk voor de opvang en (het organiseren van de noodzakelijke) verzorging van zijn of haar kinderen. Uitgangspun</t>
         </is>
       </c>
     </row>
@@ -3443,32 +3531,32 @@
         <v>330</v>
       </c>
       <c r="C12" t="n">
-        <v>1390</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>artikel=780; bijlage=356; begrippen=150; toelichting_artikel=50; toelichting_algemeen=30; aanhef=14; ondertekening=6; bijlage_pdf=4</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>wmo=1120; beide=138; jeugd=128; onbekend=4</t>
-        </is>
+        <v>1387</v>
+      </c>
+      <c r="D12" t="n">
+        <v>282</v>
+      </c>
+      <c r="E12" t="n">
+        <v>750</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GM1954</t>
+          <t>kern=1157; jeugd=124; twijfel=50; buiten_scope=35; waardering=18; aanbod=3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hoofdstuk 3 Gebruikelijke hulp &gt; 3.2 Definitie ‘gebruikelijke hulp’</t>
+          <t>Zuidplas</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>In de begripsbepalingen van de wet alsook de verordening, wordt het begrip ‘gebruikelijke hulp’ als volgt gedefinieerd: ‘de hulp die naar algemeen aanvaarde opvattingen in redelijkheid mag worden verwacht van de echtgenoot, ouders, inwonende kinderen of andere huisgenoten’.
-De normale, dagelijkse on</t>
+          <t>Hoofdstuk 2: Integrale benadering &gt; Artikel 8. Beoordeling eigen mogelijkheden en probleemoplossend vermogen &gt; lid 1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Een maatwerkvoorziening wordt niet verstrekt als naar het oordeel van het college uit het onderzoek blijkt dat de eigen kracht en het probleemoplossend vermogen van de inwoner en/of partner, ouders, inwonende kinderen of andere huisgenoten toereikend zijn om, zo nodig met inzet van het sociale netwe</t>
         </is>
       </c>
     </row>
@@ -3478,24 +3566,20 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>GM1719</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hoofdstuk 2. Hulpvraag &gt; 2.4 Aanvraag &gt; Artikel 2.4.2 Eigen kracht en gebruikelijke hulp &gt; lid 2</t>
+          <t>Woudenberg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2. Gebruikelijke hulp is hulp die naar algemeen aanvaarde opvattingen in redelijkheid mag worden verwacht van:
-a. de inwonende echtgenoot
-b. inwonende ouders
-c. inwonende kinderen
-d. of andere huisgenoten
-Het is de normale, dagelijkse hulp die huisgenoten elkaar onderling moeten bieden, omdat ze sam</t>
+          <t>Wmo2015</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>In de Wmo 2015 is bepaald dat de aanwezigheid van gebruikelijke hulp een reden is om geen maatwerkvoorzieningen te verstrekken (artikel 2.3.5, lid 3 van de Wmo 2015). Onder gebruikelijke hulp wordt verstaan de hulp die naar algemeen aanvaarde opvattingen in redelijkheid mag worden verwacht van de ec</t>
         </is>
       </c>
     </row>
@@ -3505,22 +3589,21 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>GM0938</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bijlage &gt; 1. Algemeen</t>
+          <t>Gooise Meren</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Algemene uitzonderingen
-Afhankelijk van de individuele situaties kan hulp, die naar algemeen aanvaarde maatstaven als gebruikelijke kan worden beschouwd hier toch niet gebruikelijk zijn.
-Bijvoorbeeld wanneer:
-• Uit onderzoek blijkt dat een huisgenoot aantoonbare beperkingen heeft op grond van een aa</t>
+          <t>Toelichting &gt; Algemeen &gt; afwegingskader &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>- De cliënt uit categorie I krijgt thuis naast de verleende mantelzorg geen professionele zorg op basis van een indicatie als bedoeld in artikel 2 lid 1 onder a tot en met d.
+- De cliënt uit categorie II en III krijgt thuis naast de verleende mantelzorg geen permanent professioneel toezicht of 24 uu</t>
         </is>
       </c>
     </row>
@@ -3530,24 +3613,22 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>GM1701</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOOFDSTUK 2 – GEBRUIKELIJKE HULP &gt; Artikel 2. Gebruikelijke Hulp &gt; lid 2</t>
+          <t>Enkhuizen</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2. Gebruikelijke Hulp is hulp die naar algemeen aanvaarde opvattingen in redelijkheid mag worden verwacht van:
-a. echtgenoot of partner;
-b. inwonende ouders;
-c. inwonende kinderen;
-d. of andere huisgenoten.
-Het betreft de normale, dagelijkse ondersteuning die huisgenoten elkaar onderling moeten bied</t>
+          <t>Hoofdstuk 1 Algemeen &gt; Artikel 5. Gebruikelijke hulp &gt; deel 1</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Gebruikelijke hulp wordt in de Wmo 2015 wettekst als volgt gedefinieerd:
+Hulp die naar algemeen aanvaarde opvattingen in redelijkheid mag worden verwacht van de echtgenoot, ouders, inwonende kinderen of andere huisgenoten.
+De mogelijkheid van inzet van gebruikelijke hulp heeft tot gevolg dat voor di</t>
         </is>
       </c>
     </row>
@@ -3557,19 +3638,24 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>GM0175</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Artikel 18 Financiële tegemoetkoming eigen auto en taxi Financiële tegemoetkoming eigen auto en taxi &gt; lid 2</t>
+          <t>Rijswijk (ZH.)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2. Voor zover de vervoersbehoeften van gezinsleden (gehuwden, samenwonende partners, ouder en minderjarig kind of twee inwonende kinderen) niet samenvallen, wordt in totaal niet meer dan anderhalf maal een enkele voorziening toegekend, als bedoeld in lid 1 van dit artikel.</t>
+          <t>HOOFDSTUK 1. DEFININTIE &gt; Artikel 1. Definitiebepalingen &gt; lid 2</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aanvullend wordt in deze verordening en de daarop berustende bepalingen verstaan onder:
+a. algemeen gebruikelijke voorziening is een voorziening die:
+1. niet specifiek bedoeld is voor personen met een beperking;
+2. daadwerkelijk beschikbaar is;
+3. een passende bijdrage levert aan het realiseren van </t>
         </is>
       </c>
     </row>
@@ -3584,7 +3670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3595,35 +3681,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_gemeenten</t>
+          <t>n_gemeenten_corpus</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>n_passages</t>
+          <t>n_passages_corpus</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sectietype_verdeling</t>
+          <t>n_gemeenten_filter</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>domein_verdeling</t>
+          <t>n_passages_filter</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>categorie_verdeling (heel corpus)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>voorbeeld_gemeente</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>voorbeeld_pad</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>voorbeeld_tekst</t>
         </is>
@@ -3641,92 +3732,86 @@
       <c r="C2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>artikel=2</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>wmo=1; jeugd=1</t>
-        </is>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GM1699</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Hoofdstuk 1 Algemene bepalingen &gt; Artikel 6 Verplichtingen van de subsidieontvanger &gt; lid 2</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>De subsidieontvanger zorgt, waar mogelijk, voor samenwerking met andere gelijkgerichte voorzieningen en stemt zijn activiteiten daarop af.</t>
+          <t>aanbod=1; jeugd=1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>(geen treffers binnen FILTER)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mantelzorgagenda</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GM0450</t>
+          <t>kern=15; twijfel=2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artikel 3.</t>
+          <t>Dinkelland</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>De Jeugd- en Jongerenraad tracht de in artikel 2 genoemde taak te realiseren door:
-a. Het bevorderen van de eigen ontplooiing en activiteiten van de jongeren;
-b. samenwerking met organisaties en instellingen, die geheel of gedeeltelijk gelijkgerichte doelstellingen hebben;
-c. het coördineren van gel</t>
+          <t>Hoofdstuk 4: Ambities &gt; 4.3 Erkenning van de positie van mantelzorgers &gt; deel 2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Door meer mantelzorgers actief te erkennen kan er voor gezorgd worden dat zij zich gezien en ondersteund voelen. Dit versterkt hun draagkracht, verlaagt de drempel om hulp te vragen, en draagt bij aan een maatschappelijke beweging waarin mensen op elkaar kunnen terugvallen. Het expliciet erkennen va</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mantelzorgagenda</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>artikel=17</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>wmo=17</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>GM1963</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.Samenwerking met mantelzorgers en netwerkpartners &gt; Artikel</t>
+          <t>Hoeksche Waard</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>We hebben uit de gesprekken met inwoners geleerd dat dé mantelzorger niet bestaat. Ze dragen allemaal zorg voor een ander. Soms kortdurend maar vaak langdurig zonder het perspectief dat de ander beter wordt. Door de aard van de aandoening, de persoonlijke relatie en de context van de mantelzorg zelf</t>
+          <t>3. Op weg naar een nieuwe mantelzorgagenda &gt; Artikel 3.2 Onze ambitie en doelen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>In de Hoeksche Waard maken we de beweging naar een inclusieve, sociale en verbonden samenleving. Onze ambitie is:
+‘Iedereen kan in elke situatie mee blijven doen en het wordt mogelijk gemaakt dat mensen langer thuis kunnen blijven wonen’.
+Goede mantelzorg is daarin cruciaal. Al ervaren veel mantelzo</t>
         </is>
       </c>
     </row>
@@ -3736,20 +3821,21 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>GM1963</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1. De kaders van de nota &gt; 1.4 Het lokale kader &gt; deel 2</t>
+          <t>Hoeksche Waard</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>- Mantelzorgagenda Hoeksche Waard
-Mantelzorgers verlichten de druk op de formele zorg en helpen inwoners om langer thuis te kunnen blijven wonen. Veel mantelzorgers zijn echter overbelast. De mantelzorgagenda heeft als doel om mantelzorgers zo goed mogelijk te ondersteunen. Gemeenten zijn daartoe oo</t>
+          <t>8. Monitoring en evaluatie &gt; Artikel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>We monitoren de voortgang en effecten in samenspraak met de netwerkpartners die bij de uitvoering van de mantelzorgagenda betrokken zijn en in gesprekken met mantelzorgers. Dit beschrijven we in een jaarlijkse voortgangsrapportage.
+Bij de start van dit proces verkennen we met welke kwalitatieve en k</t>
         </is>
       </c>
     </row>
@@ -3759,19 +3845,22 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>GM1963</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9. Ambitie Zorg: &gt; Ondersteuning van mantelzorgers en vrijwilligers</t>
+          <t>Hoeksche Waard</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>De komende jaren zal het belang van mantelzorgers en vrijwilligers steeds verder toenemen in de Hoeksche Waard. Vrijwilligers en mantelzorgers beantwoorden een belangrijk deel van de hulp- en zorgvraag van inwoners. Dat betekent ook dat we als gemeente zuinig moeten zijn op onze vrijwilligers en man</t>
+          <t>7. Financiering &gt; Artikel</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Voor de implementatie en uitvoering van de mantelzorgagenda wordt het beschikbare budget in het voorkeursscenario als volgt verdeeld:
+Activiteiten | 2021 | 2022 | 2023 | 2024
+Blijk van Waardering; bestaande uit:; - cadeaubonnen € 146.488 - uitvoeringskosten (subsidie - Stichting MEE*) € 20.957 | € 1</t>
         </is>
       </c>
     </row>
@@ -3781,43 +3870,20 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>GM0183</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
+          <t>Tubbergen</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>Hoofdstuk 1: Inleiding &gt; 1.1 Aanleiding &gt; deel 2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>In de Wet maatschappelijke ondersteuning 2015 (Wmo 2015) is vastgelegd dat gemeenten verantwoordelijk zijn voor het ondersteunen en waarderen van mantelzorgers. De recente Mantelzorgagenda 2023-2026 van het ministerie van VWS benadrukt het belang van een stevige lokale ondersteuning, waarin waarderi</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>GM0183</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Hoofdstuk 4: Ambities &gt; 4.1 Strategische visievorming</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>“Een stevig en samenhangend beleid opstellen voor mantelzorg dat structureel is ingebed in het sociaal domein van de gemeente Tubbergen.”
-Waarom is deze ambitie belangrijk?
-Zowel uit de Startfoto mantelzorg als het behoefteonderzoek blijkt dat het huidige beleid op mantelzorg niet de juiste doelgroe</t>
         </is>
       </c>
     </row>

--- a/review/termenverkenning.xlsx
+++ b/review/termenverkenning.xlsx
@@ -2108,7 +2108,7 @@
         <v>340</v>
       </c>
       <c r="C17" t="n">
-        <v>7503</v>
+        <v>7505</v>
       </c>
       <c r="D17" t="n">
         <v>332</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>kern=5297; jeugd=1020; twijfel=495; buiten_scope=363; aanbod=328</t>
+          <t>kern=5297; jeugd=1020; twijfel=495; buiten_scope=363; aanbod=330</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
